--- a/metricv1.xlsx
+++ b/metricv1.xlsx
@@ -48667,7 +48667,7 @@
         <v>426.0</v>
       </c>
       <c r="F302" s="16" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G302" s="16" t="s">
         <v>695</v>
@@ -64970,7 +64970,7 @@
         <v>592.0</v>
       </c>
       <c r="F417" s="14" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="G417" s="14" t="s">
         <v>283</v>
@@ -64994,7 +64994,7 @@
         <v>50</v>
       </c>
       <c r="N417" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O417" s="14" t="s">
         <v>50</v>
@@ -65397,7 +65397,7 @@
         <v>593.0</v>
       </c>
       <c r="F420" s="14" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="G420" s="14" t="s">
         <v>103</v>
@@ -65421,7 +65421,7 @@
         <v>50</v>
       </c>
       <c r="N420" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O420" s="14" t="s">
         <v>50</v>
@@ -65967,7 +65967,7 @@
         <v>593.0</v>
       </c>
       <c r="F424" s="14" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="G424" s="14" t="s">
         <v>283</v>
@@ -65991,7 +65991,7 @@
         <v>50</v>
       </c>
       <c r="N424" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O424" s="14" t="s">
         <v>50</v>

--- a/metricv1.xlsx
+++ b/metricv1.xlsx
@@ -3872,7 +3872,7 @@
     <t>28.45.ipynb</t>
   </si>
   <si>
-    <t>ds^{2} = r^{2}\left[P^{2}(m)\,dm + P^{-2}(m)\,dy^{2} - 2\,dm\,du\right] + r^{2}P^{-2}(m-r^{-1})\,du^{2} - 2\,dr\,du</t>
+    <t>ds^{2} = r^{2}\left[P^{2}(m)\,dm^{2} + P^{-2}(m)\,dy^{2} - 2\,dm\,du\right] + r^{2}P^{-2}(m-r^{-1})\,du^{2} - 2\,dr\,du</t>
   </si>
   <si>
     <t>28.46</t>
@@ -5210,7 +5210,7 @@
     <t>38.3.ipynb</t>
   </si>
   <si>
-    <t>ds^{2} = 2 \frac{(dx^{2} + dy^{2})}{(\lambda x)^{2}} - 2\,du \left[ dv + 2v\,dx/x + \frac{4x}{3\lambda}\,dy + 2x^{4} \right]</t>
+    <t>ds^{2} = 2 \frac{(dx^{2} + dy^{2})}{(\lambda x)^{2}} - 2\,du \left[ dv + 2v\,dx/x + \frac{4x}{3\lambda}\,dy + 2x^{4}\,du \right]</t>
   </si>
   <si>
     <t>Kerr-Newman Spacetime</t>
@@ -24570,7 +24570,7 @@
         <v>283</v>
       </c>
       <c r="H132" s="14" t="s">
-        <v>401</v>
+        <v>69</v>
       </c>
       <c r="I132" s="15"/>
       <c r="J132" s="14" t="s">
@@ -24598,7 +24598,7 @@
         <v>50</v>
       </c>
       <c r="R132" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S132" s="14" t="s">
         <v>51</v>
@@ -52938,7 +52938,7 @@
         <v>50</v>
       </c>
       <c r="S332" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T332" s="14" t="s">
         <v>50</v>

--- a/metricv1.xlsx
+++ b/metricv1.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15804" uniqueCount="1753">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15804" uniqueCount="1751">
   <si>
     <t>Kank</t>
   </si>
@@ -1087,7 +1087,7 @@
     <t>13.70</t>
   </si>
   <si>
-    <t>Type II</t>
+    <t>Type I (Type II in book)</t>
   </si>
   <si>
     <t>$\delta=1, \; \epsilon=1$</t>
@@ -1135,7 +1135,7 @@
     <t>13.72.pdf</t>
   </si>
   <si>
-    <t>13.72_ipynb</t>
+    <t>13.72.ipynb</t>
   </si>
   <si>
     <t>ds^{2} = \tfrac{4}{3}t^{2}\,dx^{2} + t(e^{-2x}dy^{2} + e^{2x}dz^{2}) - dt^{2}, \quad \sqrt{\kappa_{0}}\,\Phi_{1} = 1/2t</t>
@@ -2582,9 +2582,6 @@
     <t>Kota-Perjes Solutions</t>
   </si>
   <si>
-    <t>Type I (Type II in book)</t>
-  </si>
-  <si>
     <t>18.48.pdf</t>
   </si>
   <si>
@@ -2933,19 +2930,19 @@
     <t>ds^{2} = N^{-2}(z)\left[dz^{2} + G^{-1}(x)\,dx^{2} + G(x)\,d\varphi^{2} - x^{2}(dt + nx^{-2}\,d\varphi)^{2}\right]</t>
   </si>
   <si>
-    <t>21.61_e-1.pdf</t>
+    <t>21.61-e-1.pdf</t>
   </si>
   <si>
     <t>21.61_e-1.ipynb</t>
   </si>
   <si>
-    <t>21.61_e0.pdf</t>
+    <t>21.61-e0.pdf</t>
   </si>
   <si>
     <t>21.61_e0.ipynb</t>
   </si>
   <si>
-    <t>21.61_e1.pdf</t>
+    <t>21.61-e1.pdf</t>
   </si>
   <si>
     <t>21.61_e1.ipynb</t>
@@ -3104,10 +3101,10 @@
     <t>22.27a</t>
   </si>
   <si>
-    <t>22.27.a.pdf</t>
-  </si>
-  <si>
-    <t>22.27.a.ipynb</t>
+    <t>22.27a.pdf</t>
+  </si>
+  <si>
+    <t>22.27a.ipynb</t>
   </si>
   <si>
     <t>ds^{2} = e^{2(\beta+\chi+\delta)}d\rho^{2}+e^{2\beta}d\varphi^{2}+e^{2\chi}dz^{2}-e^{2\delta}dt^{2}</t>
@@ -3218,6 +3215,9 @@
     <t>22.64a</t>
   </si>
   <si>
+    <t>Type II</t>
+  </si>
+  <si>
     <t>22.64a.pdf</t>
   </si>
   <si>
@@ -4007,19 +4007,19 @@
     <t>28.59</t>
   </si>
   <si>
-    <t>28.59_e-1.pdf</t>
-  </si>
-  <si>
-    <t>28.59_e-1.ipynb</t>
+    <t>28.59_1.pdf</t>
+  </si>
+  <si>
+    <t>28.59_1.ipynb</t>
   </si>
   <si>
     <t>ds^{2} = \frac{2r^{2}\,d\zeta\,d\bar{\zeta}}{\left(1+\tfrac{1}{2}\varepsilon\zeta\bar{\zeta}\right)^{2}} - 2\,du\,dr + \left(\frac{2m_{0}+2\kappa_{0}A}{r} - \varepsilon - \frac{\kappa_{0}Q\bar{Q}}{2r^{2}}\right)du^{2}</t>
   </si>
   <si>
-    <t>28.59_e1.pdf</t>
-  </si>
-  <si>
-    <t>28.59_e1.ipynb</t>
+    <t>28.59_2.pdf</t>
+  </si>
+  <si>
+    <t>28.59_2.ipynb</t>
   </si>
   <si>
     <t>28.74</t>
@@ -4490,7 +4490,7 @@
     <t>35.30</t>
   </si>
   <si>
-    <t>Type II (Type N in book )</t>
+    <t>Type III (Type N in book )</t>
   </si>
   <si>
     <t>35.30.pdf</t>
@@ -4502,9 +4502,6 @@
     <t>ds^{2} = 2k^{-2}(1+\varepsilon\zeta\bar{\zeta})^{-2}(d\zeta+b\,du)(d\bar{\zeta}+\bar{b}\,du) - 2\,du\left[dv + du(\varepsilon k^{2}v^{2}+lv+H)\right]</t>
   </si>
   <si>
-    <t>Type III (Type N in book )</t>
-  </si>
-  <si>
     <t>35.30_e0.pdf</t>
   </si>
   <si>
@@ -4523,9 +4520,6 @@
     <t>35.30_e-1.ipynb</t>
   </si>
   <si>
-    <t>n zr</t>
-  </si>
-  <si>
     <t>35.34</t>
   </si>
   <si>
@@ -4580,7 +4574,7 @@
     <t>35.74.pdf</t>
   </si>
   <si>
-    <t>35.74.ipynb</t>
+    <t>35.74 .ipynb</t>
   </si>
   <si>
     <t>ds^{2} = \frac{dr^{2}+(2n^{2}-1)^{-1}r^{2}(d\vartheta^{2}+\sin^{2}\vartheta\,d\varphi^{2})-dt^{2}}{ar^{1+n}+br^{1-n}}</t>
@@ -4751,16 +4745,16 @@
     <t>ds^{2} = (x^{4})^{-2}\left[\eta_{\alpha\beta}\,dx^{\alpha}\,dx^{\beta} + \varepsilon n^{2}(w,x^{4})(dx^{4})^{2}\right], \quad \eta_{\alpha\beta} = \mathrm{diag}(1,1,-\varepsilon)</t>
   </si>
   <si>
-    <t>36.20a_e1.pdf</t>
-  </si>
-  <si>
-    <t>36.20a_e1.ipynb</t>
-  </si>
-  <si>
-    <t>36.20a_e-1.pdf</t>
-  </si>
-  <si>
-    <t>36.20a_e-1.ipynb</t>
+    <t>36.20a_1.pdf</t>
+  </si>
+  <si>
+    <t>36.20a_1.ipynb</t>
+  </si>
+  <si>
+    <t>36.20a_2.pdf</t>
+  </si>
+  <si>
+    <t>36.20a_2.ipynb</t>
   </si>
   <si>
     <t>36.23</t>
@@ -34497,7 +34491,7 @@
         <v>282.0</v>
       </c>
       <c r="F202" s="14" t="s">
-        <v>856</v>
+        <v>358</v>
       </c>
       <c r="G202" s="14" t="s">
         <v>845</v>
@@ -34507,11 +34501,11 @@
       </c>
       <c r="I202" s="15"/>
       <c r="J202" s="14" t="s">
+        <v>856</v>
+      </c>
+      <c r="K202" s="14" t="s">
         <v>857</v>
       </c>
-      <c r="K202" s="14" t="s">
-        <v>858</v>
-      </c>
       <c r="L202" s="14" t="s">
         <v>52</v>
       </c>
@@ -34594,7 +34588,7 @@
         <v>50</v>
       </c>
       <c r="AM202" s="14" t="s">
-        <v>856</v>
+        <v>358</v>
       </c>
       <c r="AN202" s="14" t="s">
         <v>848</v>
@@ -34603,7 +34597,7 @@
         <v>310</v>
       </c>
       <c r="AP202" s="17" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="AQ202" s="12"/>
       <c r="AR202" s="12"/>
@@ -34628,7 +34622,7 @@
     <row r="203" ht="15.75" customHeight="1">
       <c r="A203" s="40"/>
       <c r="B203" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C203" s="14" t="s">
         <v>855</v>
@@ -34640,7 +34634,7 @@
         <v>282.0</v>
       </c>
       <c r="F203" s="14" t="s">
-        <v>856</v>
+        <v>358</v>
       </c>
       <c r="G203" s="14" t="s">
         <v>845</v>
@@ -34650,11 +34644,11 @@
       </c>
       <c r="I203" s="28"/>
       <c r="J203" s="14" t="s">
+        <v>860</v>
+      </c>
+      <c r="K203" s="14" t="s">
         <v>861</v>
       </c>
-      <c r="K203" s="14" t="s">
-        <v>862</v>
-      </c>
       <c r="L203" s="14" t="s">
         <v>52</v>
       </c>
@@ -34737,7 +34731,7 @@
         <v>50</v>
       </c>
       <c r="AM203" s="14" t="s">
-        <v>856</v>
+        <v>358</v>
       </c>
       <c r="AN203" s="14" t="s">
         <v>848</v>
@@ -34746,7 +34740,7 @@
         <v>310</v>
       </c>
       <c r="AP203" s="17" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="AQ203" s="12"/>
       <c r="AR203" s="12"/>
@@ -34771,7 +34765,7 @@
     <row r="204" ht="15.75" customHeight="1">
       <c r="A204" s="40"/>
       <c r="B204" s="14" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="C204" s="14" t="s">
         <v>855</v>
@@ -34783,7 +34777,7 @@
         <v>282.0</v>
       </c>
       <c r="F204" s="41" t="s">
-        <v>856</v>
+        <v>358</v>
       </c>
       <c r="G204" s="14" t="s">
         <v>695</v>
@@ -34793,11 +34787,11 @@
       </c>
       <c r="I204" s="28"/>
       <c r="J204" s="14" t="s">
+        <v>864</v>
+      </c>
+      <c r="K204" s="14" t="s">
         <v>865</v>
       </c>
-      <c r="K204" s="14" t="s">
-        <v>866</v>
-      </c>
       <c r="L204" s="14" t="s">
         <v>52</v>
       </c>
@@ -34880,7 +34874,7 @@
         <v>52</v>
       </c>
       <c r="AM204" s="41" t="s">
-        <v>856</v>
+        <v>358</v>
       </c>
       <c r="AN204" s="14" t="s">
         <v>699</v>
@@ -34889,7 +34883,7 @@
         <v>96</v>
       </c>
       <c r="AP204" s="17" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="AQ204" s="12"/>
       <c r="AR204" s="12"/>
@@ -34914,7 +34908,7 @@
     <row r="205" ht="15.75" customHeight="1">
       <c r="A205" s="18"/>
       <c r="B205" s="14" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="C205" s="15"/>
       <c r="D205" s="16" t="s">
@@ -34934,10 +34928,10 @@
       </c>
       <c r="I205" s="15"/>
       <c r="J205" s="14" t="s">
+        <v>868</v>
+      </c>
+      <c r="K205" s="14" t="s">
         <v>869</v>
-      </c>
-      <c r="K205" s="14" t="s">
-        <v>870</v>
       </c>
       <c r="L205" s="14" t="s">
         <v>52</v>
@@ -35030,7 +35024,7 @@
         <v>89</v>
       </c>
       <c r="AP205" s="17" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="AQ205" s="12"/>
       <c r="AR205" s="12"/>
@@ -35055,7 +35049,7 @@
     <row r="206" ht="15.75" customHeight="1">
       <c r="A206" s="13"/>
       <c r="B206" s="16" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C206" s="26"/>
       <c r="D206" s="16" t="s">
@@ -35075,10 +35069,10 @@
       </c>
       <c r="I206" s="26"/>
       <c r="J206" s="16" t="s">
+        <v>872</v>
+      </c>
+      <c r="K206" s="16" t="s">
         <v>873</v>
-      </c>
-      <c r="K206" s="16" t="s">
-        <v>874</v>
       </c>
       <c r="L206" s="16">
         <v>0.0</v>
@@ -35171,7 +35165,7 @@
         <v>146</v>
       </c>
       <c r="AP206" s="17" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="AQ206" s="12"/>
       <c r="AR206" s="12"/>
@@ -35196,7 +35190,7 @@
     <row r="207">
       <c r="A207" s="18"/>
       <c r="B207" s="16" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="C207" s="26"/>
       <c r="D207" s="16" t="s">
@@ -35216,10 +35210,10 @@
       </c>
       <c r="I207" s="26"/>
       <c r="J207" s="16" t="s">
+        <v>876</v>
+      </c>
+      <c r="K207" s="16" t="s">
         <v>877</v>
-      </c>
-      <c r="K207" s="16" t="s">
-        <v>878</v>
       </c>
       <c r="L207" s="16" t="s">
         <v>51</v>
@@ -35312,7 +35306,7 @@
         <v>146</v>
       </c>
       <c r="AP207" s="17" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="AQ207" s="12"/>
       <c r="AR207" s="12"/>
@@ -35337,7 +35331,7 @@
     <row r="208">
       <c r="A208" s="18"/>
       <c r="B208" s="16" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="C208" s="26"/>
       <c r="D208" s="16" t="s">
@@ -35356,13 +35350,13 @@
         <v>146</v>
       </c>
       <c r="I208" s="16" t="s">
+        <v>879</v>
+      </c>
+      <c r="J208" s="16" t="s">
         <v>880</v>
       </c>
-      <c r="J208" s="16" t="s">
+      <c r="K208" s="16" t="s">
         <v>881</v>
-      </c>
-      <c r="K208" s="16" t="s">
-        <v>882</v>
       </c>
       <c r="L208" s="16" t="s">
         <v>51</v>
@@ -35455,7 +35449,7 @@
         <v>146</v>
       </c>
       <c r="AP208" s="17" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="AQ208" s="12"/>
       <c r="AR208" s="12"/>
@@ -35480,7 +35474,7 @@
     <row r="209">
       <c r="A209" s="18"/>
       <c r="B209" s="16" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="C209" s="26"/>
       <c r="D209" s="16" t="s">
@@ -35499,13 +35493,13 @@
         <v>146</v>
       </c>
       <c r="I209" s="16" t="s">
+        <v>882</v>
+      </c>
+      <c r="J209" s="16" t="s">
         <v>883</v>
       </c>
-      <c r="J209" s="16" t="s">
+      <c r="K209" s="16" t="s">
         <v>884</v>
-      </c>
-      <c r="K209" s="16" t="s">
-        <v>885</v>
       </c>
       <c r="L209" s="16" t="s">
         <v>51</v>
@@ -35598,7 +35592,7 @@
         <v>146</v>
       </c>
       <c r="AP209" s="17" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="AQ209" s="12"/>
       <c r="AR209" s="12"/>
@@ -35623,7 +35617,7 @@
     <row r="210">
       <c r="A210" s="18"/>
       <c r="B210" s="16" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="C210" s="26"/>
       <c r="D210" s="16" t="s">
@@ -35642,13 +35636,13 @@
         <v>146</v>
       </c>
       <c r="I210" s="16" t="s">
+        <v>885</v>
+      </c>
+      <c r="J210" s="16" t="s">
         <v>886</v>
       </c>
-      <c r="J210" s="16" t="s">
+      <c r="K210" s="16" t="s">
         <v>887</v>
-      </c>
-      <c r="K210" s="16" t="s">
-        <v>888</v>
       </c>
       <c r="L210" s="16" t="s">
         <v>51</v>
@@ -35741,7 +35735,7 @@
         <v>146</v>
       </c>
       <c r="AP210" s="17" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="AQ210" s="12"/>
       <c r="AR210" s="12"/>
@@ -35766,7 +35760,7 @@
     <row r="211" ht="15.75" customHeight="1">
       <c r="A211" s="13"/>
       <c r="B211" s="16" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C211" s="26"/>
       <c r="D211" s="16" t="s">
@@ -35786,10 +35780,10 @@
       </c>
       <c r="I211" s="26"/>
       <c r="J211" s="16" t="s">
+        <v>889</v>
+      </c>
+      <c r="K211" s="16" t="s">
         <v>890</v>
-      </c>
-      <c r="K211" s="16" t="s">
-        <v>891</v>
       </c>
       <c r="L211" s="16" t="s">
         <v>51</v>
@@ -35882,7 +35876,7 @@
         <v>146</v>
       </c>
       <c r="AP211" s="17" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="AQ211" s="12"/>
       <c r="AR211" s="12"/>
@@ -35907,7 +35901,7 @@
     <row r="212" ht="15.75" customHeight="1">
       <c r="A212" s="18"/>
       <c r="B212" s="14" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="C212" s="15"/>
       <c r="D212" s="16" t="s">
@@ -35927,10 +35921,10 @@
       </c>
       <c r="I212" s="15"/>
       <c r="J212" s="14" t="s">
+        <v>893</v>
+      </c>
+      <c r="K212" s="14" t="s">
         <v>894</v>
-      </c>
-      <c r="K212" s="14" t="s">
-        <v>895</v>
       </c>
       <c r="L212" s="14" t="s">
         <v>52</v>
@@ -36023,7 +36017,7 @@
         <v>146</v>
       </c>
       <c r="AP212" s="17" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="AQ212" s="12"/>
       <c r="AR212" s="12"/>
@@ -36048,7 +36042,7 @@
     <row r="213" ht="15.75" customHeight="1">
       <c r="A213" s="13"/>
       <c r="B213" s="14" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="C213" s="15"/>
       <c r="D213" s="16" t="s">
@@ -36068,10 +36062,10 @@
       </c>
       <c r="I213" s="15"/>
       <c r="J213" s="14" t="s">
+        <v>897</v>
+      </c>
+      <c r="K213" s="14" t="s">
         <v>898</v>
-      </c>
-      <c r="K213" s="14" t="s">
-        <v>899</v>
       </c>
       <c r="L213" s="14" t="s">
         <v>51</v>
@@ -36164,7 +36158,7 @@
         <v>89</v>
       </c>
       <c r="AP213" s="17" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="AQ213" s="12"/>
       <c r="AR213" s="12"/>
@@ -36189,7 +36183,7 @@
     <row r="214" ht="15.75" customHeight="1">
       <c r="A214" s="18"/>
       <c r="B214" s="14" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="C214" s="15"/>
       <c r="D214" s="16" t="s">
@@ -36209,10 +36203,10 @@
       </c>
       <c r="I214" s="15"/>
       <c r="J214" s="14" t="s">
+        <v>901</v>
+      </c>
+      <c r="K214" s="14" t="s">
         <v>902</v>
-      </c>
-      <c r="K214" s="14" t="s">
-        <v>903</v>
       </c>
       <c r="L214" s="14" t="s">
         <v>52</v>
@@ -36305,7 +36299,7 @@
         <v>89</v>
       </c>
       <c r="AP214" s="17" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="AQ214" s="12"/>
       <c r="AR214" s="12"/>
@@ -36330,7 +36324,7 @@
     <row r="215" ht="15.75" customHeight="1">
       <c r="A215" s="13"/>
       <c r="B215" s="14" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C215" s="15"/>
       <c r="D215" s="16" t="s">
@@ -36350,10 +36344,10 @@
       </c>
       <c r="I215" s="15"/>
       <c r="J215" s="14" t="s">
+        <v>905</v>
+      </c>
+      <c r="K215" s="14" t="s">
         <v>906</v>
-      </c>
-      <c r="K215" s="14" t="s">
-        <v>907</v>
       </c>
       <c r="L215" s="14" t="s">
         <v>52</v>
@@ -36446,7 +36440,7 @@
         <v>310</v>
       </c>
       <c r="AP215" s="17" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="AQ215" s="12"/>
       <c r="AR215" s="12"/>
@@ -36471,10 +36465,10 @@
     <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="18"/>
       <c r="B216" s="14" t="s">
+        <v>907</v>
+      </c>
+      <c r="C216" s="14" t="s">
         <v>908</v>
-      </c>
-      <c r="C216" s="14" t="s">
-        <v>909</v>
       </c>
       <c r="D216" s="16" t="s">
         <v>43</v>
@@ -36493,10 +36487,10 @@
       </c>
       <c r="I216" s="15"/>
       <c r="J216" s="14" t="s">
+        <v>909</v>
+      </c>
+      <c r="K216" s="14" t="s">
         <v>910</v>
-      </c>
-      <c r="K216" s="14" t="s">
-        <v>911</v>
       </c>
       <c r="L216" s="14" t="s">
         <v>50</v>
@@ -36589,7 +36583,7 @@
         <v>96</v>
       </c>
       <c r="AP216" s="17" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="AQ216" s="12"/>
       <c r="AR216" s="12"/>
@@ -36614,7 +36608,7 @@
     <row r="217" ht="15.75" customHeight="1">
       <c r="A217" s="13"/>
       <c r="B217" s="14" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C217" s="15"/>
       <c r="D217" s="16" t="s">
@@ -36634,10 +36628,10 @@
       </c>
       <c r="I217" s="15"/>
       <c r="J217" s="14" t="s">
+        <v>913</v>
+      </c>
+      <c r="K217" s="14" t="s">
         <v>914</v>
-      </c>
-      <c r="K217" s="14" t="s">
-        <v>915</v>
       </c>
       <c r="L217" s="14" t="s">
         <v>51</v>
@@ -36730,7 +36724,7 @@
         <v>310</v>
       </c>
       <c r="AP217" s="34" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="AQ217" s="12"/>
       <c r="AR217" s="12"/>
@@ -36755,7 +36749,7 @@
     <row r="218" ht="15.75" customHeight="1">
       <c r="A218" s="42"/>
       <c r="B218" s="43" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C218" s="43"/>
       <c r="D218" s="44" t="s">
@@ -36775,10 +36769,10 @@
       </c>
       <c r="I218" s="46"/>
       <c r="J218" s="47" t="s">
+        <v>917</v>
+      </c>
+      <c r="K218" s="48" t="s">
         <v>918</v>
-      </c>
-      <c r="K218" s="48" t="s">
-        <v>919</v>
       </c>
       <c r="L218" s="43" t="s">
         <v>52</v>
@@ -36871,7 +36865,7 @@
         <v>89</v>
       </c>
       <c r="AP218" s="50" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="AQ218" s="34"/>
       <c r="AR218" s="12"/>
@@ -36896,7 +36890,7 @@
     <row r="219" ht="15.75" customHeight="1">
       <c r="A219" s="13"/>
       <c r="B219" s="14" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C219" s="15"/>
       <c r="D219" s="16" t="s">
@@ -36916,10 +36910,10 @@
       </c>
       <c r="I219" s="15"/>
       <c r="J219" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="K219" s="14" t="s">
         <v>922</v>
-      </c>
-      <c r="K219" s="14" t="s">
-        <v>923</v>
       </c>
       <c r="L219" s="14" t="s">
         <v>50</v>
@@ -37012,7 +37006,7 @@
         <v>89</v>
       </c>
       <c r="AP219" s="34" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="AQ219" s="12"/>
       <c r="AR219" s="12"/>
@@ -37037,7 +37031,7 @@
     <row r="220" ht="15.75" customHeight="1">
       <c r="A220" s="13"/>
       <c r="B220" s="14" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="C220" s="15"/>
       <c r="D220" s="16" t="s">
@@ -37057,10 +37051,10 @@
       </c>
       <c r="I220" s="15"/>
       <c r="J220" s="14" t="s">
+        <v>925</v>
+      </c>
+      <c r="K220" s="14" t="s">
         <v>926</v>
-      </c>
-      <c r="K220" s="14" t="s">
-        <v>927</v>
       </c>
       <c r="L220" s="14" t="s">
         <v>50</v>
@@ -37153,7 +37147,7 @@
         <v>89</v>
       </c>
       <c r="AP220" s="34" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="AQ220" s="12"/>
       <c r="AR220" s="12"/>
@@ -37178,7 +37172,7 @@
     <row r="221" ht="15.75" customHeight="1">
       <c r="A221" s="13"/>
       <c r="B221" s="14" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="C221" s="15"/>
       <c r="D221" s="16" t="s">
@@ -37198,10 +37192,10 @@
       </c>
       <c r="I221" s="15"/>
       <c r="J221" s="14" t="s">
+        <v>929</v>
+      </c>
+      <c r="K221" s="14" t="s">
         <v>930</v>
-      </c>
-      <c r="K221" s="14" t="s">
-        <v>931</v>
       </c>
       <c r="L221" s="14" t="s">
         <v>50</v>
@@ -37294,7 +37288,7 @@
         <v>89</v>
       </c>
       <c r="AP221" s="34" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="AQ221" s="12"/>
       <c r="AR221" s="12"/>
@@ -37319,10 +37313,10 @@
     <row r="222" ht="15.75" customHeight="1">
       <c r="A222" s="51"/>
       <c r="B222" s="14" t="s">
+        <v>932</v>
+      </c>
+      <c r="C222" s="14" t="s">
         <v>933</v>
-      </c>
-      <c r="C222" s="14" t="s">
-        <v>934</v>
       </c>
       <c r="D222" s="16" t="s">
         <v>43</v>
@@ -37331,7 +37325,7 @@
         <v>326.0</v>
       </c>
       <c r="F222" s="14" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="G222" s="14" t="s">
         <v>695</v>
@@ -37341,11 +37335,11 @@
       </c>
       <c r="I222" s="15"/>
       <c r="J222" s="14" t="s">
+        <v>935</v>
+      </c>
+      <c r="K222" s="14" t="s">
         <v>936</v>
       </c>
-      <c r="K222" s="14" t="s">
-        <v>937</v>
-      </c>
       <c r="L222" s="14" t="s">
         <v>52</v>
       </c>
@@ -37428,7 +37422,7 @@
         <v>52</v>
       </c>
       <c r="AM222" s="14" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="AN222" s="14" t="s">
         <v>699</v>
@@ -37437,7 +37431,7 @@
         <v>89</v>
       </c>
       <c r="AP222" s="17" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="AQ222" s="12"/>
       <c r="AR222" s="12"/>
@@ -37462,10 +37456,10 @@
     <row r="223" ht="15.75" customHeight="1">
       <c r="A223" s="13"/>
       <c r="B223" s="14" t="s">
+        <v>938</v>
+      </c>
+      <c r="C223" s="14" t="s">
         <v>939</v>
-      </c>
-      <c r="C223" s="14" t="s">
-        <v>940</v>
       </c>
       <c r="D223" s="16" t="s">
         <v>43</v>
@@ -37484,10 +37478,10 @@
       </c>
       <c r="I223" s="15"/>
       <c r="J223" s="14" t="s">
+        <v>940</v>
+      </c>
+      <c r="K223" s="14" t="s">
         <v>941</v>
-      </c>
-      <c r="K223" s="14" t="s">
-        <v>942</v>
       </c>
       <c r="L223" s="14" t="s">
         <v>52</v>
@@ -37580,7 +37574,7 @@
         <v>89</v>
       </c>
       <c r="AP223" s="17" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="AQ223" s="12"/>
       <c r="AR223" s="12"/>
@@ -37605,10 +37599,10 @@
     <row r="224" ht="15.75" customHeight="1">
       <c r="A224" s="13"/>
       <c r="B224" s="14" t="s">
+        <v>938</v>
+      </c>
+      <c r="C224" s="14" t="s">
         <v>939</v>
-      </c>
-      <c r="C224" s="14" t="s">
-        <v>940</v>
       </c>
       <c r="D224" s="16" t="s">
         <v>43</v>
@@ -37629,10 +37623,10 @@
         <v>270</v>
       </c>
       <c r="J224" s="14" t="s">
+        <v>943</v>
+      </c>
+      <c r="K224" s="14" t="s">
         <v>944</v>
-      </c>
-      <c r="K224" s="14" t="s">
-        <v>945</v>
       </c>
       <c r="L224" s="14" t="s">
         <v>52</v>
@@ -37725,7 +37719,7 @@
         <v>89</v>
       </c>
       <c r="AP224" s="17" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="AQ224" s="12"/>
       <c r="AR224" s="12"/>
@@ -37750,10 +37744,10 @@
     <row r="225" ht="15.75" customHeight="1">
       <c r="A225" s="13"/>
       <c r="B225" s="14" t="s">
+        <v>938</v>
+      </c>
+      <c r="C225" s="14" t="s">
         <v>939</v>
-      </c>
-      <c r="C225" s="14" t="s">
-        <v>940</v>
       </c>
       <c r="D225" s="16" t="s">
         <v>43</v>
@@ -37774,10 +37768,10 @@
         <v>264</v>
       </c>
       <c r="J225" s="14" t="s">
+        <v>946</v>
+      </c>
+      <c r="K225" s="14" t="s">
         <v>947</v>
-      </c>
-      <c r="K225" s="14" t="s">
-        <v>948</v>
       </c>
       <c r="L225" s="14" t="s">
         <v>52</v>
@@ -37870,7 +37864,7 @@
         <v>89</v>
       </c>
       <c r="AP225" s="17" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="AQ225" s="12"/>
       <c r="AR225" s="12"/>
@@ -37895,10 +37889,10 @@
     <row r="226" ht="15.75" customHeight="1">
       <c r="A226" s="13"/>
       <c r="B226" s="14" t="s">
+        <v>938</v>
+      </c>
+      <c r="C226" s="14" t="s">
         <v>939</v>
-      </c>
-      <c r="C226" s="14" t="s">
-        <v>940</v>
       </c>
       <c r="D226" s="16" t="s">
         <v>43</v>
@@ -37919,10 +37913,10 @@
         <v>267</v>
       </c>
       <c r="J226" s="14" t="s">
+        <v>949</v>
+      </c>
+      <c r="K226" s="14" t="s">
         <v>950</v>
-      </c>
-      <c r="K226" s="14" t="s">
-        <v>951</v>
       </c>
       <c r="L226" s="14" t="s">
         <v>52</v>
@@ -38015,7 +38009,7 @@
         <v>89</v>
       </c>
       <c r="AP226" s="17" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="AQ226" s="12"/>
       <c r="AR226" s="12"/>
@@ -38040,7 +38034,7 @@
     <row r="227" ht="15.75" customHeight="1">
       <c r="A227" s="18"/>
       <c r="B227" s="14" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="C227" s="15"/>
       <c r="D227" s="16" t="s">
@@ -38060,10 +38054,10 @@
       </c>
       <c r="I227" s="15"/>
       <c r="J227" s="14" t="s">
+        <v>953</v>
+      </c>
+      <c r="K227" s="14" t="s">
         <v>954</v>
-      </c>
-      <c r="K227" s="14" t="s">
-        <v>955</v>
       </c>
       <c r="L227" s="14" t="s">
         <v>50</v>
@@ -38156,7 +38150,7 @@
         <v>89</v>
       </c>
       <c r="AP227" s="17" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="AQ227" s="12"/>
       <c r="AR227" s="12"/>
@@ -38181,7 +38175,7 @@
     <row r="228" ht="15.75" customHeight="1">
       <c r="A228" s="13"/>
       <c r="B228" s="14" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="C228" s="15"/>
       <c r="D228" s="16" t="s">
@@ -38201,10 +38195,10 @@
       </c>
       <c r="I228" s="15"/>
       <c r="J228" s="14" t="s">
+        <v>957</v>
+      </c>
+      <c r="K228" s="14" t="s">
         <v>958</v>
-      </c>
-      <c r="K228" s="14" t="s">
-        <v>959</v>
       </c>
       <c r="L228" s="14" t="s">
         <v>52</v>
@@ -38297,7 +38291,7 @@
         <v>89</v>
       </c>
       <c r="AP228" s="17" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="AQ228" s="12"/>
       <c r="AR228" s="12"/>
@@ -38322,7 +38316,7 @@
     <row r="229" ht="15.75" customHeight="1">
       <c r="A229" s="18"/>
       <c r="B229" s="14" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="C229" s="15"/>
       <c r="D229" s="16" t="s">
@@ -38342,10 +38336,10 @@
       </c>
       <c r="I229" s="15"/>
       <c r="J229" s="14" t="s">
+        <v>961</v>
+      </c>
+      <c r="K229" s="14" t="s">
         <v>962</v>
-      </c>
-      <c r="K229" s="14" t="s">
-        <v>963</v>
       </c>
       <c r="L229" s="14" t="s">
         <v>52</v>
@@ -38438,7 +38432,7 @@
         <v>146</v>
       </c>
       <c r="AP229" s="17" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="AQ229" s="12"/>
       <c r="AR229" s="12"/>
@@ -38463,7 +38457,7 @@
     <row r="230" ht="15.75" customHeight="1">
       <c r="A230" s="18"/>
       <c r="B230" s="14" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="C230" s="15"/>
       <c r="D230" s="16" t="s">
@@ -38483,10 +38477,10 @@
       </c>
       <c r="I230" s="15"/>
       <c r="J230" s="14" t="s">
+        <v>965</v>
+      </c>
+      <c r="K230" s="14" t="s">
         <v>966</v>
-      </c>
-      <c r="K230" s="14" t="s">
-        <v>967</v>
       </c>
       <c r="L230" s="14" t="s">
         <v>52</v>
@@ -38579,7 +38573,7 @@
         <v>146</v>
       </c>
       <c r="AP230" s="17" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="AQ230" s="12"/>
       <c r="AR230" s="12"/>
@@ -38604,7 +38598,7 @@
     <row r="231" ht="15.75" customHeight="1">
       <c r="A231" s="18"/>
       <c r="B231" s="14" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="C231" s="15"/>
       <c r="D231" s="16" t="s">
@@ -38624,10 +38618,10 @@
       </c>
       <c r="I231" s="15"/>
       <c r="J231" s="14" t="s">
+        <v>969</v>
+      </c>
+      <c r="K231" s="14" t="s">
         <v>970</v>
-      </c>
-      <c r="K231" s="14" t="s">
-        <v>971</v>
       </c>
       <c r="L231" s="14" t="s">
         <v>51</v>
@@ -38720,7 +38714,7 @@
         <v>146</v>
       </c>
       <c r="AP231" s="17" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="AQ231" s="12"/>
       <c r="AR231" s="12"/>
@@ -38745,7 +38739,7 @@
     <row r="232" ht="15.75" customHeight="1">
       <c r="A232" s="18"/>
       <c r="B232" s="14" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="C232" s="15"/>
       <c r="D232" s="16" t="s">
@@ -38767,10 +38761,10 @@
         <v>165</v>
       </c>
       <c r="J232" s="14" t="s">
+        <v>972</v>
+      </c>
+      <c r="K232" s="14" t="s">
         <v>973</v>
-      </c>
-      <c r="K232" s="14" t="s">
-        <v>974</v>
       </c>
       <c r="L232" s="14" t="s">
         <v>51</v>
@@ -38863,7 +38857,7 @@
         <v>146</v>
       </c>
       <c r="AP232" s="17" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="AQ232" s="12"/>
       <c r="AR232" s="12"/>
@@ -38888,7 +38882,7 @@
     <row r="233" ht="15.75" customHeight="1">
       <c r="A233" s="18"/>
       <c r="B233" s="14" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="C233" s="15"/>
       <c r="D233" s="16" t="s">
@@ -38910,10 +38904,10 @@
         <v>90</v>
       </c>
       <c r="J233" s="14" t="s">
+        <v>974</v>
+      </c>
+      <c r="K233" s="14" t="s">
         <v>975</v>
-      </c>
-      <c r="K233" s="14" t="s">
-        <v>976</v>
       </c>
       <c r="L233" s="14" t="s">
         <v>51</v>
@@ -39006,7 +39000,7 @@
         <v>146</v>
       </c>
       <c r="AP233" s="17" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="AQ233" s="12"/>
       <c r="AR233" s="12"/>
@@ -39031,7 +39025,7 @@
     <row r="234" ht="15.75" customHeight="1">
       <c r="A234" s="18"/>
       <c r="B234" s="14" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="C234" s="15"/>
       <c r="D234" s="16" t="s">
@@ -39053,10 +39047,10 @@
         <v>85</v>
       </c>
       <c r="J234" s="14" t="s">
+        <v>976</v>
+      </c>
+      <c r="K234" s="14" t="s">
         <v>977</v>
-      </c>
-      <c r="K234" s="14" t="s">
-        <v>978</v>
       </c>
       <c r="L234" s="14" t="s">
         <v>51</v>
@@ -39149,7 +39143,7 @@
         <v>146</v>
       </c>
       <c r="AP234" s="17" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="AQ234" s="12"/>
       <c r="AR234" s="12"/>
@@ -39174,7 +39168,7 @@
     <row r="235" ht="15.75" customHeight="1">
       <c r="A235" s="18"/>
       <c r="B235" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="C235" s="15"/>
       <c r="D235" s="16" t="s">
@@ -39194,10 +39188,10 @@
       </c>
       <c r="I235" s="15"/>
       <c r="J235" s="14" t="s">
+        <v>979</v>
+      </c>
+      <c r="K235" s="14" t="s">
         <v>980</v>
-      </c>
-      <c r="K235" s="14" t="s">
-        <v>981</v>
       </c>
       <c r="L235" s="14" t="s">
         <v>51</v>
@@ -39290,7 +39284,7 @@
         <v>146</v>
       </c>
       <c r="AP235" s="17" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="AQ235" s="12"/>
       <c r="AR235" s="12"/>
@@ -39315,7 +39309,7 @@
     <row r="236" ht="15.75" customHeight="1">
       <c r="A236" s="13"/>
       <c r="B236" s="38" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="C236" s="26"/>
       <c r="D236" s="16" t="s">
@@ -39335,10 +39329,10 @@
       </c>
       <c r="I236" s="26"/>
       <c r="J236" s="16" t="s">
+        <v>983</v>
+      </c>
+      <c r="K236" s="16" t="s">
         <v>984</v>
-      </c>
-      <c r="K236" s="16" t="s">
-        <v>985</v>
       </c>
       <c r="L236" s="16">
         <v>0.0</v>
@@ -39431,7 +39425,7 @@
         <v>96</v>
       </c>
       <c r="AP236" s="17" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="AQ236" s="12"/>
       <c r="AR236" s="12"/>
@@ -39456,7 +39450,7 @@
     <row r="237" ht="15.75" customHeight="1">
       <c r="A237" s="13"/>
       <c r="B237" s="38" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="C237" s="26"/>
       <c r="D237" s="16" t="s">
@@ -39476,10 +39470,10 @@
       </c>
       <c r="I237" s="26"/>
       <c r="J237" s="16" t="s">
+        <v>987</v>
+      </c>
+      <c r="K237" s="16" t="s">
         <v>988</v>
-      </c>
-      <c r="K237" s="16" t="s">
-        <v>989</v>
       </c>
       <c r="L237" s="16" t="s">
         <v>51</v>
@@ -39572,7 +39566,7 @@
         <v>310</v>
       </c>
       <c r="AP237" s="17" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="AQ237" s="12"/>
       <c r="AR237" s="12"/>
@@ -39597,7 +39591,7 @@
     <row r="238" ht="15.75" customHeight="1">
       <c r="A238" s="13"/>
       <c r="B238" s="14" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="C238" s="15"/>
       <c r="D238" s="16" t="s">
@@ -39616,13 +39610,13 @@
         <v>96</v>
       </c>
       <c r="I238" s="14" t="s">
+        <v>991</v>
+      </c>
+      <c r="J238" s="14" t="s">
         <v>992</v>
       </c>
-      <c r="J238" s="14" t="s">
+      <c r="K238" s="14" t="s">
         <v>993</v>
-      </c>
-      <c r="K238" s="14" t="s">
-        <v>994</v>
       </c>
       <c r="L238" s="14" t="s">
         <v>51</v>
@@ -39715,7 +39709,7 @@
         <v>96</v>
       </c>
       <c r="AP238" s="17" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="AQ238" s="12"/>
       <c r="AR238" s="12"/>
@@ -39740,7 +39734,7 @@
     <row r="239" ht="15.75" customHeight="1">
       <c r="A239" s="13"/>
       <c r="B239" s="14" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="C239" s="15"/>
       <c r="D239" s="16" t="s">
@@ -39760,10 +39754,10 @@
       </c>
       <c r="I239" s="15"/>
       <c r="J239" s="14" t="s">
+        <v>996</v>
+      </c>
+      <c r="K239" s="14" t="s">
         <v>997</v>
-      </c>
-      <c r="K239" s="14" t="s">
-        <v>998</v>
       </c>
       <c r="L239" s="14" t="s">
         <v>51</v>
@@ -39856,7 +39850,7 @@
         <v>89</v>
       </c>
       <c r="AP239" s="17" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="AQ239" s="12"/>
       <c r="AR239" s="12"/>
@@ -39881,7 +39875,7 @@
     <row r="240" ht="15.75" customHeight="1">
       <c r="A240" s="13"/>
       <c r="B240" s="14" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="C240" s="15"/>
       <c r="D240" s="16" t="s">
@@ -39901,10 +39895,10 @@
       </c>
       <c r="I240" s="15"/>
       <c r="J240" s="14" t="s">
+        <v>1000</v>
+      </c>
+      <c r="K240" s="14" t="s">
         <v>1001</v>
-      </c>
-      <c r="K240" s="14" t="s">
-        <v>1002</v>
       </c>
       <c r="L240" s="14" t="s">
         <v>52</v>
@@ -39997,7 +39991,7 @@
         <v>89</v>
       </c>
       <c r="AP240" s="17" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="AQ240" s="12"/>
       <c r="AR240" s="12"/>
@@ -40022,10 +40016,10 @@
     <row r="241" ht="15.75" customHeight="1">
       <c r="A241" s="13"/>
       <c r="B241" s="14" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C241" s="14" t="s">
         <v>1004</v>
-      </c>
-      <c r="C241" s="14" t="s">
-        <v>1005</v>
       </c>
       <c r="D241" s="16" t="s">
         <v>43</v>
@@ -40044,10 +40038,10 @@
       </c>
       <c r="I241" s="15"/>
       <c r="J241" s="14" t="s">
+        <v>1005</v>
+      </c>
+      <c r="K241" s="14" t="s">
         <v>1006</v>
-      </c>
-      <c r="K241" s="14" t="s">
-        <v>1007</v>
       </c>
       <c r="L241" s="14" t="s">
         <v>50</v>
@@ -40140,7 +40134,7 @@
         <v>89</v>
       </c>
       <c r="AP241" s="17" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="AQ241" s="12"/>
       <c r="AR241" s="12"/>
@@ -40165,7 +40159,7 @@
     <row r="242" ht="15.75" customHeight="1">
       <c r="A242" s="13"/>
       <c r="B242" s="16" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="C242" s="52"/>
       <c r="D242" s="20" t="s">
@@ -40185,10 +40179,10 @@
       </c>
       <c r="I242" s="26"/>
       <c r="J242" s="16" t="s">
+        <v>1009</v>
+      </c>
+      <c r="K242" s="16" t="s">
         <v>1010</v>
-      </c>
-      <c r="K242" s="16" t="s">
-        <v>1011</v>
       </c>
       <c r="L242" s="16" t="s">
         <v>51</v>
@@ -40281,7 +40275,7 @@
         <v>89</v>
       </c>
       <c r="AP242" s="17" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="AQ242" s="12"/>
       <c r="AR242" s="12"/>
@@ -40306,7 +40300,7 @@
     <row r="243" ht="15.0" customHeight="1">
       <c r="A243" s="13"/>
       <c r="B243" s="16" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="C243" s="53"/>
       <c r="D243" s="16" t="s">
@@ -40326,10 +40320,10 @@
       </c>
       <c r="I243" s="26"/>
       <c r="J243" s="16" t="s">
+        <v>1013</v>
+      </c>
+      <c r="K243" s="16" t="s">
         <v>1014</v>
-      </c>
-      <c r="K243" s="16" t="s">
-        <v>1015</v>
       </c>
       <c r="L243" s="16" t="s">
         <v>51</v>
@@ -40422,7 +40416,7 @@
         <v>89</v>
       </c>
       <c r="AP243" s="17" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="AQ243" s="12"/>
       <c r="AR243" s="12"/>
@@ -40447,7 +40441,7 @@
     <row r="244" ht="15.75" customHeight="1">
       <c r="A244" s="18"/>
       <c r="B244" s="16" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C244" s="26"/>
       <c r="D244" s="16" t="s">
@@ -40467,10 +40461,10 @@
       </c>
       <c r="I244" s="26"/>
       <c r="J244" s="16" t="s">
+        <v>1017</v>
+      </c>
+      <c r="K244" s="16" t="s">
         <v>1018</v>
-      </c>
-      <c r="K244" s="16" t="s">
-        <v>1019</v>
       </c>
       <c r="L244" s="16" t="s">
         <v>51</v>
@@ -40563,7 +40557,7 @@
         <v>89</v>
       </c>
       <c r="AP244" s="17" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="AQ244" s="12"/>
       <c r="AR244" s="12"/>
@@ -40588,7 +40582,7 @@
     <row r="245" ht="15.75" customHeight="1">
       <c r="A245" s="18"/>
       <c r="B245" s="14" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="C245" s="15"/>
       <c r="D245" s="16" t="s">
@@ -40608,10 +40602,10 @@
       </c>
       <c r="I245" s="15"/>
       <c r="J245" s="14" t="s">
+        <v>1021</v>
+      </c>
+      <c r="K245" s="14" t="s">
         <v>1022</v>
-      </c>
-      <c r="K245" s="14" t="s">
-        <v>1023</v>
       </c>
       <c r="L245" s="14" t="s">
         <v>51</v>
@@ -40704,7 +40698,7 @@
         <v>89</v>
       </c>
       <c r="AP245" s="17" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="AQ245" s="12"/>
       <c r="AR245" s="12"/>
@@ -40729,7 +40723,7 @@
     <row r="246" ht="15.75" customHeight="1">
       <c r="A246" s="13"/>
       <c r="B246" s="14" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="C246" s="15"/>
       <c r="D246" s="16" t="s">
@@ -40749,10 +40743,10 @@
       </c>
       <c r="I246" s="15"/>
       <c r="J246" s="14" t="s">
+        <v>1025</v>
+      </c>
+      <c r="K246" s="14" t="s">
         <v>1026</v>
-      </c>
-      <c r="K246" s="14" t="s">
-        <v>1027</v>
       </c>
       <c r="L246" s="14" t="s">
         <v>51</v>
@@ -40845,7 +40839,7 @@
         <v>401</v>
       </c>
       <c r="AP246" s="17" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AQ246" s="12"/>
       <c r="AR246" s="12"/>
@@ -40870,7 +40864,7 @@
     <row r="247" ht="15.75" customHeight="1">
       <c r="A247" s="18"/>
       <c r="B247" s="14" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="C247" s="15"/>
       <c r="D247" s="16" t="s">
@@ -40890,10 +40884,10 @@
       </c>
       <c r="I247" s="15"/>
       <c r="J247" s="14" t="s">
+        <v>1029</v>
+      </c>
+      <c r="K247" s="14" t="s">
         <v>1030</v>
-      </c>
-      <c r="K247" s="14" t="s">
-        <v>1031</v>
       </c>
       <c r="L247" s="14" t="s">
         <v>51</v>
@@ -40986,7 +40980,7 @@
         <v>146</v>
       </c>
       <c r="AP247" s="17" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="AQ247" s="12"/>
       <c r="AR247" s="12"/>
@@ -41011,7 +41005,7 @@
     <row r="248" ht="15.75" customHeight="1">
       <c r="A248" s="18"/>
       <c r="B248" s="14" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="C248" s="15"/>
       <c r="D248" s="16" t="s">
@@ -41031,10 +41025,10 @@
       </c>
       <c r="I248" s="15"/>
       <c r="J248" s="14" t="s">
+        <v>1033</v>
+      </c>
+      <c r="K248" s="14" t="s">
         <v>1034</v>
-      </c>
-      <c r="K248" s="14" t="s">
-        <v>1035</v>
       </c>
       <c r="L248" s="14" t="s">
         <v>51</v>
@@ -41127,7 +41121,7 @@
         <v>146</v>
       </c>
       <c r="AP248" s="17" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="AQ248" s="12"/>
       <c r="AR248" s="12"/>
@@ -41152,7 +41146,7 @@
     <row r="249" ht="15.75" customHeight="1">
       <c r="A249" s="13"/>
       <c r="B249" s="14" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="C249" s="15"/>
       <c r="D249" s="16" t="s">
@@ -41172,10 +41166,10 @@
       </c>
       <c r="I249" s="15"/>
       <c r="J249" s="14" t="s">
+        <v>1037</v>
+      </c>
+      <c r="K249" s="14" t="s">
         <v>1038</v>
-      </c>
-      <c r="K249" s="14" t="s">
-        <v>1039</v>
       </c>
       <c r="L249" s="14" t="s">
         <v>52</v>
@@ -41268,7 +41262,7 @@
         <v>146</v>
       </c>
       <c r="AP249" s="17" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="AQ249" s="12"/>
       <c r="AR249" s="12"/>
@@ -41293,7 +41287,7 @@
     <row r="250" ht="15.75" customHeight="1">
       <c r="A250" s="18"/>
       <c r="B250" s="14" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="C250" s="15"/>
       <c r="D250" s="16" t="s">
@@ -41313,10 +41307,10 @@
       </c>
       <c r="I250" s="15"/>
       <c r="J250" s="14" t="s">
+        <v>1041</v>
+      </c>
+      <c r="K250" s="14" t="s">
         <v>1042</v>
-      </c>
-      <c r="K250" s="14" t="s">
-        <v>1043</v>
       </c>
       <c r="L250" s="14" t="s">
         <v>51</v>
@@ -41409,7 +41403,7 @@
         <v>146</v>
       </c>
       <c r="AP250" s="17" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="AQ250" s="12"/>
       <c r="AR250" s="12"/>
@@ -41434,7 +41428,7 @@
     <row r="251" ht="15.75" customHeight="1">
       <c r="A251" s="13"/>
       <c r="B251" s="14" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="C251" s="15"/>
       <c r="D251" s="16" t="s">
@@ -41454,10 +41448,10 @@
       </c>
       <c r="I251" s="15"/>
       <c r="J251" s="14" t="s">
+        <v>1045</v>
+      </c>
+      <c r="K251" s="14" t="s">
         <v>1046</v>
-      </c>
-      <c r="K251" s="14" t="s">
-        <v>1047</v>
       </c>
       <c r="L251" s="16" t="s">
         <v>52</v>
@@ -41550,7 +41544,7 @@
         <v>310</v>
       </c>
       <c r="AP251" s="17" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="AQ251" s="12"/>
       <c r="AR251" s="12"/>
@@ -41575,7 +41569,7 @@
     <row r="252" ht="15.75" customHeight="1">
       <c r="A252" s="18"/>
       <c r="B252" s="14" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C252" s="15"/>
       <c r="D252" s="16" t="s">
@@ -41595,34 +41589,34 @@
       </c>
       <c r="I252" s="15"/>
       <c r="J252" s="14" t="s">
+        <v>1049</v>
+      </c>
+      <c r="K252" s="14" t="s">
         <v>1050</v>
       </c>
-      <c r="K252" s="14" t="s">
+      <c r="L252" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="M252" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="N252" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="O252" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="P252" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q252" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="R252" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="S252" s="14" t="s">
         <v>1051</v>
-      </c>
-      <c r="L252" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="M252" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="N252" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="O252" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="P252" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q252" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="R252" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="S252" s="14" t="s">
-        <v>1052</v>
       </c>
       <c r="T252" s="14" t="s">
         <v>50</v>
@@ -41691,7 +41685,7 @@
         <v>310</v>
       </c>
       <c r="AP252" s="34" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="AQ252" s="12"/>
       <c r="AR252" s="12"/>
@@ -41716,7 +41710,7 @@
     <row r="253" ht="15.75" customHeight="1">
       <c r="A253" s="18"/>
       <c r="B253" s="14" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="C253" s="15"/>
       <c r="D253" s="16" t="s">
@@ -41736,10 +41730,10 @@
       </c>
       <c r="I253" s="15"/>
       <c r="J253" s="14" t="s">
+        <v>1054</v>
+      </c>
+      <c r="K253" s="14" t="s">
         <v>1055</v>
-      </c>
-      <c r="K253" s="14" t="s">
-        <v>1056</v>
       </c>
       <c r="L253" s="14" t="s">
         <v>52</v>
@@ -41832,7 +41826,7 @@
         <v>310</v>
       </c>
       <c r="AP253" s="17" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="AQ253" s="12"/>
       <c r="AR253" s="12"/>
@@ -41857,7 +41851,7 @@
     <row r="254" ht="15.75" customHeight="1">
       <c r="A254" s="13"/>
       <c r="B254" s="14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="C254" s="15"/>
       <c r="D254" s="16" t="s">
@@ -41876,13 +41870,13 @@
         <v>89</v>
       </c>
       <c r="I254" s="14" t="s">
+        <v>1058</v>
+      </c>
+      <c r="J254" s="14" t="s">
         <v>1059</v>
       </c>
-      <c r="J254" s="14" t="s">
+      <c r="K254" s="14" t="s">
         <v>1060</v>
-      </c>
-      <c r="K254" s="14" t="s">
-        <v>1061</v>
       </c>
       <c r="L254" s="14" t="s">
         <v>51</v>
@@ -41975,7 +41969,7 @@
         <v>89</v>
       </c>
       <c r="AP254" s="17" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="AQ254" s="12"/>
       <c r="AR254" s="12"/>
@@ -42000,7 +41994,7 @@
     <row r="255" ht="15.75" customHeight="1">
       <c r="A255" s="13"/>
       <c r="B255" s="16" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="C255" s="26"/>
       <c r="D255" s="16" t="s">
@@ -42020,10 +42014,10 @@
       </c>
       <c r="I255" s="26"/>
       <c r="J255" s="16" t="s">
+        <v>1063</v>
+      </c>
+      <c r="K255" s="16" t="s">
         <v>1064</v>
-      </c>
-      <c r="K255" s="16" t="s">
-        <v>1065</v>
       </c>
       <c r="L255" s="16">
         <v>0.0</v>
@@ -42116,7 +42110,7 @@
         <v>89</v>
       </c>
       <c r="AP255" s="17" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="AQ255" s="12"/>
       <c r="AR255" s="12"/>
@@ -42141,7 +42135,7 @@
     <row r="256" ht="15.75" customHeight="1">
       <c r="A256" s="13"/>
       <c r="B256" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="C256" s="15"/>
       <c r="D256" s="16" t="s">
@@ -42151,7 +42145,7 @@
         <v>356.0</v>
       </c>
       <c r="F256" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="G256" s="14" t="s">
         <v>695</v>
@@ -42248,7 +42242,7 @@
         <v>50</v>
       </c>
       <c r="AM256" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="AN256" s="14" t="s">
         <v>699</v>
@@ -42433,7 +42427,7 @@
         <v>359.0</v>
       </c>
       <c r="F258" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="G258" s="14" t="s">
         <v>283</v>
@@ -42532,7 +42526,7 @@
         <v>50</v>
       </c>
       <c r="AM258" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="AN258" s="14" t="s">
         <v>286</v>
@@ -45964,7 +45958,7 @@
         <v>381.0</v>
       </c>
       <c r="F283" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="G283" s="14" t="s">
         <v>845</v>
@@ -46061,7 +46055,7 @@
         <v>52</v>
       </c>
       <c r="AM283" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="AN283" s="14" t="s">
         <v>848</v>
@@ -47799,7 +47793,7 @@
         <v>423.0</v>
       </c>
       <c r="F296" s="16" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="G296" s="14" t="s">
         <v>1224</v>
@@ -47898,7 +47892,7 @@
         <v>52</v>
       </c>
       <c r="AM296" s="16" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="AN296" s="14" t="s">
         <v>1227</v>
@@ -48655,7 +48649,7 @@
         <v>427.0</v>
       </c>
       <c r="F302" s="16" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="G302" s="16" t="s">
         <v>695</v>
@@ -48752,7 +48746,7 @@
         <v>51</v>
       </c>
       <c r="AM302" s="16" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="AN302" s="16" t="s">
         <v>699</v>
@@ -49930,7 +49924,7 @@
         <v>431.0</v>
       </c>
       <c r="F311" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="G311" s="14" t="s">
         <v>1224</v>
@@ -50027,7 +50021,7 @@
         <v>52</v>
       </c>
       <c r="AM311" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="AN311" s="14" t="s">
         <v>1227</v>
@@ -50071,7 +50065,7 @@
         <v>431.0</v>
       </c>
       <c r="F312" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="G312" s="14" t="s">
         <v>103</v>
@@ -50168,7 +50162,7 @@
         <v>52</v>
       </c>
       <c r="AM312" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="AN312" s="14" t="s">
         <v>106</v>
@@ -50212,7 +50206,7 @@
         <v>432.0</v>
       </c>
       <c r="F313" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="G313" s="14" t="s">
         <v>695</v>
@@ -50309,7 +50303,7 @@
         <v>51</v>
       </c>
       <c r="AM313" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="AN313" s="14" t="s">
         <v>699</v>
@@ -50353,7 +50347,7 @@
         <v>432.0</v>
       </c>
       <c r="F314" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="G314" s="14" t="s">
         <v>845</v>
@@ -50450,7 +50444,7 @@
         <v>51</v>
       </c>
       <c r="AM314" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="AN314" s="14" t="s">
         <v>848</v>
@@ -50494,7 +50488,7 @@
         <v>432.0</v>
       </c>
       <c r="F315" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="G315" s="14" t="s">
         <v>845</v>
@@ -50591,7 +50585,7 @@
         <v>51</v>
       </c>
       <c r="AM315" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="AN315" s="14" t="s">
         <v>848</v>
@@ -50635,7 +50629,7 @@
         <v>432.0</v>
       </c>
       <c r="F316" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="G316" s="14" t="s">
         <v>845</v>
@@ -50734,7 +50728,7 @@
         <v>51</v>
       </c>
       <c r="AM316" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="AN316" s="14" t="s">
         <v>848</v>
@@ -50778,7 +50772,7 @@
         <v>432.0</v>
       </c>
       <c r="F317" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="G317" s="14" t="s">
         <v>845</v>
@@ -50877,7 +50871,7 @@
         <v>51</v>
       </c>
       <c r="AM317" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="AN317" s="14" t="s">
         <v>848</v>
@@ -50921,7 +50915,7 @@
         <v>432.0</v>
       </c>
       <c r="F318" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="G318" s="14" t="s">
         <v>845</v>
@@ -51018,7 +51012,7 @@
         <v>51</v>
       </c>
       <c r="AM318" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="AN318" s="14" t="s">
         <v>848</v>
@@ -51062,7 +51056,7 @@
         <v>432.0</v>
       </c>
       <c r="F319" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="G319" s="14" t="s">
         <v>845</v>
@@ -51159,7 +51153,7 @@
         <v>51</v>
       </c>
       <c r="AM319" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="AN319" s="14" t="s">
         <v>848</v>
@@ -51203,7 +51197,7 @@
         <v>433.0</v>
       </c>
       <c r="F320" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="G320" s="14" t="s">
         <v>845</v>
@@ -51300,7 +51294,7 @@
         <v>51</v>
       </c>
       <c r="AM320" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="AN320" s="14" t="s">
         <v>848</v>
@@ -51344,7 +51338,7 @@
         <v>433.0</v>
       </c>
       <c r="F321" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="G321" s="14" t="s">
         <v>845</v>
@@ -51441,7 +51435,7 @@
         <v>51</v>
       </c>
       <c r="AM321" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="AN321" s="14" t="s">
         <v>848</v>
@@ -51485,7 +51479,7 @@
         <v>433.0</v>
       </c>
       <c r="F322" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="G322" s="14" t="s">
         <v>845</v>
@@ -51582,7 +51576,7 @@
         <v>52</v>
       </c>
       <c r="AM322" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="AN322" s="14" t="s">
         <v>848</v>
@@ -51626,7 +51620,7 @@
         <v>433.0</v>
       </c>
       <c r="F323" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="G323" s="14" t="s">
         <v>1224</v>
@@ -51725,7 +51719,7 @@
         <v>52</v>
       </c>
       <c r="AM323" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="AN323" s="14" t="s">
         <v>1227</v>
@@ -51769,7 +51763,7 @@
         <v>433.0</v>
       </c>
       <c r="F324" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="G324" s="14" t="s">
         <v>1224</v>
@@ -51868,7 +51862,7 @@
         <v>52</v>
       </c>
       <c r="AM324" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="AN324" s="14" t="s">
         <v>1227</v>
@@ -52053,7 +52047,7 @@
         <v>436.0</v>
       </c>
       <c r="F326" s="16" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="G326" s="16" t="s">
         <v>1224</v>
@@ -52150,7 +52144,7 @@
         <v>52</v>
       </c>
       <c r="AM326" s="16" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="AN326" s="16" t="s">
         <v>1227</v>
@@ -52194,7 +52188,7 @@
         <v>436.0</v>
       </c>
       <c r="F327" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="G327" s="14" t="s">
         <v>1224</v>
@@ -52293,7 +52287,7 @@
         <v>52</v>
       </c>
       <c r="AM327" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="AN327" s="14" t="s">
         <v>1227</v>
@@ -52760,7 +52754,7 @@
         <v>471.0</v>
       </c>
       <c r="F331" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="G331" s="14" t="s">
         <v>1224</v>
@@ -52857,7 +52851,7 @@
         <v>52</v>
       </c>
       <c r="AM331" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="AN331" s="14" t="s">
         <v>1227</v>
@@ -53324,7 +53318,7 @@
         <v>478.0</v>
       </c>
       <c r="F335" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="G335" s="14" t="s">
         <v>103</v>
@@ -53421,7 +53415,7 @@
         <v>52</v>
       </c>
       <c r="AM335" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="AN335" s="14" t="s">
         <v>106</v>
@@ -53465,7 +53459,7 @@
         <v>478.0</v>
       </c>
       <c r="F336" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="G336" s="14" t="s">
         <v>103</v>
@@ -53564,7 +53558,7 @@
         <v>52</v>
       </c>
       <c r="AM336" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="AN336" s="14" t="s">
         <v>106</v>
@@ -53608,7 +53602,7 @@
         <v>478.0</v>
       </c>
       <c r="F337" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="G337" s="14" t="s">
         <v>103</v>
@@ -53707,7 +53701,7 @@
         <v>52</v>
       </c>
       <c r="AM337" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="AN337" s="14" t="s">
         <v>106</v>
@@ -53751,7 +53745,7 @@
         <v>478.0</v>
       </c>
       <c r="F338" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="G338" s="14" t="s">
         <v>103</v>
@@ -53850,7 +53844,7 @@
         <v>52</v>
       </c>
       <c r="AM338" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="AN338" s="14" t="s">
         <v>106</v>
@@ -53894,7 +53888,7 @@
         <v>479.0</v>
       </c>
       <c r="F339" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="G339" s="14" t="s">
         <v>845</v>
@@ -53991,7 +53985,7 @@
         <v>52</v>
       </c>
       <c r="AM339" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="AN339" s="14" t="s">
         <v>848</v>
@@ -54176,7 +54170,7 @@
         <v>482.0</v>
       </c>
       <c r="F341" s="59" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="G341" s="41" t="s">
         <v>1224</v>
@@ -54275,7 +54269,7 @@
         <v>52</v>
       </c>
       <c r="AM341" s="59" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="AN341" s="41" t="s">
         <v>1227</v>
@@ -55030,7 +55024,7 @@
         <v>508.0</v>
       </c>
       <c r="F347" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="G347" s="14" t="s">
         <v>845</v>
@@ -55039,7 +55033,7 @@
         <v>1146</v>
       </c>
       <c r="I347" s="14" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="J347" s="14" t="s">
         <v>1422</v>
@@ -55129,7 +55123,7 @@
         <v>51</v>
       </c>
       <c r="AM347" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="AN347" s="14" t="s">
         <v>848</v>
@@ -55173,7 +55167,7 @@
         <v>508.0</v>
       </c>
       <c r="F348" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="G348" s="14" t="s">
         <v>845</v>
@@ -55272,7 +55266,7 @@
         <v>51</v>
       </c>
       <c r="AM348" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="AN348" s="14" t="s">
         <v>848</v>
@@ -55316,7 +55310,7 @@
         <v>509.0</v>
       </c>
       <c r="F349" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="G349" s="14" t="s">
         <v>695</v>
@@ -55413,7 +55407,7 @@
         <v>51</v>
       </c>
       <c r="AM349" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="AN349" s="14" t="s">
         <v>699</v>
@@ -55457,7 +55451,7 @@
         <v>509.0</v>
       </c>
       <c r="F350" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="G350" s="14" t="s">
         <v>845</v>
@@ -55554,7 +55548,7 @@
         <v>52</v>
       </c>
       <c r="AM350" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="AN350" s="14" t="s">
         <v>848</v>
@@ -55598,7 +55592,7 @@
         <v>510.0</v>
       </c>
       <c r="F351" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="G351" s="41" t="s">
         <v>1224</v>
@@ -55695,7 +55689,7 @@
         <v>50</v>
       </c>
       <c r="AM351" s="14" t="s">
-        <v>358</v>
+        <v>1067</v>
       </c>
       <c r="AN351" s="41" t="s">
         <v>1227</v>
@@ -55880,7 +55874,7 @@
         <v>513.0</v>
       </c>
       <c r="F353" s="61" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="G353" s="14" t="s">
         <v>1224</v>
@@ -55977,7 +55971,7 @@
         <v>52</v>
       </c>
       <c r="AM353" s="61" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="AN353" s="14" t="s">
         <v>1227</v>
@@ -57892,7 +57886,7 @@
         <v>50</v>
       </c>
       <c r="N367" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O367" s="14" t="s">
         <v>52</v>
@@ -57928,7 +57922,7 @@
         <v>52</v>
       </c>
       <c r="Z367" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AA367" s="14" t="s">
         <v>50</v>
@@ -58011,7 +58005,7 @@
         <v>558.0</v>
       </c>
       <c r="F368" s="62" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="G368" s="14" t="s">
         <v>1224</v>
@@ -58023,11 +58017,11 @@
         <v>90</v>
       </c>
       <c r="J368" s="14" t="s">
+        <v>1496</v>
+      </c>
+      <c r="K368" s="14" t="s">
         <v>1497</v>
       </c>
-      <c r="K368" s="14" t="s">
-        <v>1498</v>
-      </c>
       <c r="L368" s="14" t="s">
         <v>50</v>
       </c>
@@ -58110,7 +58104,7 @@
         <v>52</v>
       </c>
       <c r="AM368" s="62" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="AN368" s="14" t="s">
         <v>1227</v>
@@ -58166,11 +58160,11 @@
         <v>85</v>
       </c>
       <c r="J369" s="14" t="s">
+        <v>1498</v>
+      </c>
+      <c r="K369" s="14" t="s">
         <v>1499</v>
       </c>
-      <c r="K369" s="14" t="s">
-        <v>1500</v>
-      </c>
       <c r="L369" s="14" t="s">
         <v>50</v>
       </c>
@@ -58178,7 +58172,7 @@
         <v>50</v>
       </c>
       <c r="N369" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O369" s="14" t="s">
         <v>52</v>
@@ -58214,7 +58208,7 @@
         <v>52</v>
       </c>
       <c r="Z369" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AA369" s="14" t="s">
         <v>50</v>
@@ -58309,11 +58303,11 @@
         <v>165</v>
       </c>
       <c r="J370" s="14" t="s">
+        <v>1500</v>
+      </c>
+      <c r="K370" s="14" t="s">
         <v>1501</v>
       </c>
-      <c r="K370" s="14" t="s">
-        <v>1502</v>
-      </c>
       <c r="L370" s="14" t="s">
         <v>50</v>
       </c>
@@ -58321,7 +58315,7 @@
         <v>50</v>
       </c>
       <c r="N370" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O370" s="14" t="s">
         <v>52</v>
@@ -58357,7 +58351,7 @@
         <v>52</v>
       </c>
       <c r="Z370" s="14" t="s">
-        <v>1503</v>
+        <v>50</v>
       </c>
       <c r="AA370" s="14" t="s">
         <v>50</v>
@@ -58430,7 +58424,7 @@
     <row r="371" ht="15.75" customHeight="1">
       <c r="A371" s="13"/>
       <c r="B371" s="14" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="C371" s="15"/>
       <c r="D371" s="16" t="s">
@@ -58450,10 +58444,10 @@
       </c>
       <c r="I371" s="15"/>
       <c r="J371" s="14" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="K371" s="14" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="L371" s="14" t="s">
         <v>50</v>
@@ -58546,7 +58540,7 @@
         <v>89</v>
       </c>
       <c r="AP371" s="17" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="AQ371" s="12"/>
       <c r="AR371" s="12"/>
@@ -58571,7 +58565,7 @@
     <row r="372" ht="15.75" customHeight="1">
       <c r="A372" s="13"/>
       <c r="B372" s="14" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="C372" s="15"/>
       <c r="D372" s="16" t="s">
@@ -58593,10 +58587,10 @@
         <v>165</v>
       </c>
       <c r="J372" s="14" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="K372" s="14" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="L372" s="14" t="s">
         <v>50</v>
@@ -58689,7 +58683,7 @@
         <v>89</v>
       </c>
       <c r="AP372" s="17" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="AQ372" s="12"/>
       <c r="AR372" s="12"/>
@@ -58714,7 +58708,7 @@
     <row r="373" ht="15.75" customHeight="1">
       <c r="A373" s="13"/>
       <c r="B373" s="14" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="C373" s="15"/>
       <c r="D373" s="16" t="s">
@@ -58736,10 +58730,10 @@
         <v>85</v>
       </c>
       <c r="J373" s="14" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="K373" s="14" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="L373" s="14" t="s">
         <v>50</v>
@@ -58832,7 +58826,7 @@
         <v>89</v>
       </c>
       <c r="AP373" s="17" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="AQ373" s="12"/>
       <c r="AR373" s="12"/>
@@ -58857,7 +58851,7 @@
     <row r="374" ht="15.75" customHeight="1">
       <c r="A374" s="13"/>
       <c r="B374" s="14" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="C374" s="15"/>
       <c r="D374" s="16" t="s">
@@ -58877,10 +58871,10 @@
       </c>
       <c r="I374" s="15"/>
       <c r="J374" s="14" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="K374" s="14" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="L374" s="14" t="s">
         <v>50</v>
@@ -58973,7 +58967,7 @@
         <v>89</v>
       </c>
       <c r="AP374" s="17" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="AQ374" s="12"/>
       <c r="AR374" s="12"/>
@@ -58998,7 +58992,7 @@
     <row r="375" ht="15.75" customHeight="1">
       <c r="A375" s="18"/>
       <c r="B375" s="14" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="C375" s="15"/>
       <c r="D375" s="16" t="s">
@@ -59018,10 +59012,10 @@
       </c>
       <c r="I375" s="15"/>
       <c r="J375" s="14" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="K375" s="14" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="L375" s="14" t="s">
         <v>50</v>
@@ -59114,7 +59108,7 @@
         <v>69</v>
       </c>
       <c r="AP375" s="17" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="AQ375" s="12"/>
       <c r="AR375" s="12"/>
@@ -59139,7 +59133,7 @@
     <row r="376" ht="15.75" customHeight="1">
       <c r="A376" s="13"/>
       <c r="B376" s="16" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="C376" s="26"/>
       <c r="D376" s="16" t="s">
@@ -59159,10 +59153,10 @@
       </c>
       <c r="I376" s="26"/>
       <c r="J376" s="16" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="K376" s="16" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="L376" s="16">
         <v>0.0</v>
@@ -59255,7 +59249,7 @@
         <v>146</v>
       </c>
       <c r="AP376" s="17" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="AQ376" s="12"/>
       <c r="AR376" s="12"/>
@@ -59280,7 +59274,7 @@
     <row r="377" ht="15.75" customHeight="1">
       <c r="A377" s="13"/>
       <c r="B377" s="14" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="C377" s="15"/>
       <c r="D377" s="16" t="s">
@@ -59302,10 +59296,10 @@
         <v>264</v>
       </c>
       <c r="J377" s="14" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="K377" s="14" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="L377" s="14" t="s">
         <v>50</v>
@@ -59398,7 +59392,7 @@
         <v>146</v>
       </c>
       <c r="AP377" s="17" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="AQ377" s="12"/>
       <c r="AR377" s="12"/>
@@ -59423,7 +59417,7 @@
     <row r="378" ht="15.75" customHeight="1">
       <c r="A378" s="13"/>
       <c r="B378" s="14" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="C378" s="15"/>
       <c r="D378" s="16" t="s">
@@ -59445,10 +59439,10 @@
         <v>270</v>
       </c>
       <c r="J378" s="14" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="K378" s="14" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="L378" s="14" t="s">
         <v>50</v>
@@ -59541,7 +59535,7 @@
         <v>146</v>
       </c>
       <c r="AP378" s="17" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="AQ378" s="12"/>
       <c r="AR378" s="12"/>
@@ -59566,7 +59560,7 @@
     <row r="379" ht="15.75" customHeight="1">
       <c r="A379" s="13"/>
       <c r="B379" s="14" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="C379" s="15"/>
       <c r="D379" s="16" t="s">
@@ -59585,13 +59579,13 @@
         <v>191</v>
       </c>
       <c r="I379" s="14" t="s">
+        <v>1530</v>
+      </c>
+      <c r="J379" s="14" t="s">
+        <v>1531</v>
+      </c>
+      <c r="K379" s="14" t="s">
         <v>1532</v>
-      </c>
-      <c r="J379" s="14" t="s">
-        <v>1533</v>
-      </c>
-      <c r="K379" s="14" t="s">
-        <v>1534</v>
       </c>
       <c r="L379" s="14" t="s">
         <v>50</v>
@@ -59684,7 +59678,7 @@
         <v>191</v>
       </c>
       <c r="AP379" s="17" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="AQ379" s="12"/>
       <c r="AR379" s="12"/>
@@ -59709,7 +59703,7 @@
     <row r="380" ht="15.75" customHeight="1">
       <c r="A380" s="13"/>
       <c r="B380" s="14" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="C380" s="15"/>
       <c r="D380" s="16" t="s">
@@ -59728,13 +59722,13 @@
         <v>191</v>
       </c>
       <c r="I380" s="14" t="s">
+        <v>1534</v>
+      </c>
+      <c r="J380" s="14" t="s">
+        <v>1535</v>
+      </c>
+      <c r="K380" s="14" t="s">
         <v>1536</v>
-      </c>
-      <c r="J380" s="14" t="s">
-        <v>1537</v>
-      </c>
-      <c r="K380" s="14" t="s">
-        <v>1538</v>
       </c>
       <c r="L380" s="14" t="s">
         <v>50</v>
@@ -59827,7 +59821,7 @@
         <v>191</v>
       </c>
       <c r="AP380" s="17" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="AQ380" s="12"/>
       <c r="AR380" s="12"/>
@@ -59852,7 +59846,7 @@
     <row r="381" ht="15.75" customHeight="1">
       <c r="A381" s="13"/>
       <c r="B381" s="16" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="C381" s="26"/>
       <c r="D381" s="16" t="s">
@@ -59872,10 +59866,10 @@
       </c>
       <c r="I381" s="26"/>
       <c r="J381" s="16" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="K381" s="16" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="L381" s="16" t="s">
         <v>51</v>
@@ -59968,7 +59962,7 @@
         <v>146</v>
       </c>
       <c r="AP381" s="17" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="AQ381" s="12"/>
       <c r="AR381" s="12"/>
@@ -59993,7 +59987,7 @@
     <row r="382" ht="15.75" customHeight="1">
       <c r="A382" s="18"/>
       <c r="B382" s="14" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="C382" s="15"/>
       <c r="D382" s="16" t="s">
@@ -60013,10 +60007,10 @@
       </c>
       <c r="I382" s="15"/>
       <c r="J382" s="14" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="K382" s="14" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="L382" s="14" t="s">
         <v>51</v>
@@ -60109,7 +60103,7 @@
         <v>146</v>
       </c>
       <c r="AP382" s="17" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="AQ382" s="12"/>
       <c r="AR382" s="12"/>
@@ -60134,7 +60128,7 @@
     <row r="383" ht="15.75" customHeight="1">
       <c r="A383" s="18"/>
       <c r="B383" s="14" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="C383" s="15"/>
       <c r="D383" s="16" t="s">
@@ -60154,10 +60148,10 @@
       </c>
       <c r="I383" s="15"/>
       <c r="J383" s="14" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="K383" s="14" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="L383" s="14" t="s">
         <v>50</v>
@@ -60250,7 +60244,7 @@
         <v>146</v>
       </c>
       <c r="AP383" s="17" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="AQ383" s="12"/>
       <c r="AR383" s="12"/>
@@ -60275,7 +60269,7 @@
     <row r="384" ht="15.75" customHeight="1">
       <c r="A384" s="18"/>
       <c r="B384" s="14" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="C384" s="15"/>
       <c r="D384" s="16" t="s">
@@ -60295,10 +60289,10 @@
       </c>
       <c r="I384" s="15"/>
       <c r="J384" s="14" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="K384" s="14" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="L384" s="14" t="s">
         <v>50</v>
@@ -60391,7 +60385,7 @@
         <v>89</v>
       </c>
       <c r="AP384" s="17" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
       <c r="AQ384" s="12"/>
       <c r="AR384" s="12"/>
@@ -60416,7 +60410,7 @@
     <row r="385" ht="15.75" customHeight="1">
       <c r="A385" s="13"/>
       <c r="B385" s="14" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="C385" s="15"/>
       <c r="D385" s="16" t="s">
@@ -60436,10 +60430,10 @@
       </c>
       <c r="I385" s="15"/>
       <c r="J385" s="14" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="K385" s="14" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="L385" s="14" t="s">
         <v>50</v>
@@ -60532,7 +60526,7 @@
         <v>146</v>
       </c>
       <c r="AP385" s="17" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="AQ385" s="12"/>
       <c r="AR385" s="12"/>
@@ -60557,7 +60551,7 @@
     <row r="386" ht="15.75" customHeight="1">
       <c r="A386" s="18"/>
       <c r="B386" s="14" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="C386" s="15"/>
       <c r="D386" s="16" t="s">
@@ -60577,10 +60571,10 @@
       </c>
       <c r="I386" s="15"/>
       <c r="J386" s="14" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="K386" s="14" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="L386" s="14" t="s">
         <v>52</v>
@@ -60673,7 +60667,7 @@
         <v>146</v>
       </c>
       <c r="AP386" s="17" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="AQ386" s="12"/>
       <c r="AR386" s="12"/>
@@ -60698,7 +60692,7 @@
     <row r="387" ht="15.75" customHeight="1">
       <c r="A387" s="13"/>
       <c r="B387" s="14" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="C387" s="15"/>
       <c r="D387" s="16" t="s">
@@ -60718,10 +60712,10 @@
       </c>
       <c r="I387" s="15"/>
       <c r="J387" s="14" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="K387" s="14" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="L387" s="14" t="s">
         <v>50</v>
@@ -60814,7 +60808,7 @@
         <v>146</v>
       </c>
       <c r="AP387" s="17" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="AQ387" s="12"/>
       <c r="AR387" s="12"/>
@@ -60839,7 +60833,7 @@
     <row r="388" ht="15.75" customHeight="1">
       <c r="A388" s="13"/>
       <c r="B388" s="14" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="C388" s="15"/>
       <c r="D388" s="16" t="s">
@@ -60861,10 +60855,10 @@
         <v>85</v>
       </c>
       <c r="J388" s="14" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="K388" s="14" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="L388" s="14" t="s">
         <v>50</v>
@@ -60957,7 +60951,7 @@
         <v>146</v>
       </c>
       <c r="AP388" s="17" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="AQ388" s="12"/>
       <c r="AR388" s="12"/>
@@ -60982,7 +60976,7 @@
     <row r="389" ht="15.75" customHeight="1">
       <c r="A389" s="13"/>
       <c r="B389" s="14" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="C389" s="15"/>
       <c r="D389" s="16" t="s">
@@ -61004,10 +60998,10 @@
         <v>165</v>
       </c>
       <c r="J389" s="14" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="K389" s="14" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="L389" s="14" t="s">
         <v>50</v>
@@ -61100,7 +61094,7 @@
         <v>146</v>
       </c>
       <c r="AP389" s="17" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="AQ389" s="12"/>
       <c r="AR389" s="12"/>
@@ -61125,7 +61119,7 @@
     <row r="390" ht="15.75" customHeight="1">
       <c r="A390" s="13"/>
       <c r="B390" s="16" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="C390" s="26"/>
       <c r="D390" s="16" t="s">
@@ -61145,10 +61139,10 @@
       </c>
       <c r="I390" s="26"/>
       <c r="J390" s="16" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="K390" s="16" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="L390" s="16" t="s">
         <v>52</v>
@@ -61241,7 +61235,7 @@
         <v>146</v>
       </c>
       <c r="AP390" s="17" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
       <c r="AQ390" s="12"/>
       <c r="AR390" s="12"/>
@@ -61266,7 +61260,7 @@
     <row r="391" ht="15.75" customHeight="1">
       <c r="A391" s="13"/>
       <c r="B391" s="14" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="C391" s="15"/>
       <c r="D391" s="16" t="s">
@@ -61286,10 +61280,10 @@
       </c>
       <c r="I391" s="15"/>
       <c r="J391" s="14" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
       <c r="K391" s="14" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="L391" s="14" t="s">
         <v>51</v>
@@ -61382,7 +61376,7 @@
         <v>146</v>
       </c>
       <c r="AP391" s="17" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="AQ391" s="12"/>
       <c r="AR391" s="12"/>
@@ -61407,7 +61401,7 @@
     <row r="392" ht="15.75" customHeight="1">
       <c r="A392" s="13"/>
       <c r="B392" s="14" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="C392" s="15"/>
       <c r="D392" s="16" t="s">
@@ -61429,10 +61423,10 @@
         <v>85</v>
       </c>
       <c r="J392" s="14" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="K392" s="14" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="L392" s="14" t="s">
         <v>51</v>
@@ -61525,7 +61519,7 @@
         <v>146</v>
       </c>
       <c r="AP392" s="17" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="AQ392" s="12"/>
       <c r="AR392" s="12"/>
@@ -61550,7 +61544,7 @@
     <row r="393" ht="15.75" customHeight="1">
       <c r="A393" s="13"/>
       <c r="B393" s="14" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="C393" s="15"/>
       <c r="D393" s="16" t="s">
@@ -61572,10 +61566,10 @@
         <v>165</v>
       </c>
       <c r="J393" s="14" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="K393" s="14" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="L393" s="14" t="s">
         <v>52</v>
@@ -61668,7 +61662,7 @@
         <v>146</v>
       </c>
       <c r="AP393" s="17" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="AQ393" s="12"/>
       <c r="AR393" s="12"/>
@@ -61693,7 +61687,7 @@
     <row r="394" ht="15.75" customHeight="1">
       <c r="A394" s="13"/>
       <c r="B394" s="16" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="C394" s="26"/>
       <c r="D394" s="16" t="s">
@@ -61713,10 +61707,10 @@
       </c>
       <c r="I394" s="26"/>
       <c r="J394" s="16" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="K394" s="16" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="L394" s="16">
         <v>0.0</v>
@@ -61809,7 +61803,7 @@
         <v>146</v>
       </c>
       <c r="AP394" s="17" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="AQ394" s="12"/>
       <c r="AR394" s="12"/>
@@ -61834,7 +61828,7 @@
     <row r="395" ht="15.75" customHeight="1">
       <c r="A395" s="13"/>
       <c r="B395" s="14" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="C395" s="15"/>
       <c r="D395" s="16" t="s">
@@ -61853,13 +61847,13 @@
         <v>127</v>
       </c>
       <c r="I395" s="14" t="s">
+        <v>1586</v>
+      </c>
+      <c r="J395" s="14" t="s">
+        <v>1587</v>
+      </c>
+      <c r="K395" s="14" t="s">
         <v>1588</v>
-      </c>
-      <c r="J395" s="14" t="s">
-        <v>1589</v>
-      </c>
-      <c r="K395" s="14" t="s">
-        <v>1590</v>
       </c>
       <c r="L395" s="14" t="s">
         <v>51</v>
@@ -61952,7 +61946,7 @@
         <v>127</v>
       </c>
       <c r="AP395" s="17" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="AQ395" s="12"/>
       <c r="AR395" s="12"/>
@@ -61977,7 +61971,7 @@
     <row r="396" ht="15.75" customHeight="1">
       <c r="A396" s="18"/>
       <c r="B396" s="14" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="C396" s="15"/>
       <c r="D396" s="16" t="s">
@@ -61997,10 +61991,10 @@
       </c>
       <c r="I396" s="15"/>
       <c r="J396" s="14" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="K396" s="14" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="L396" s="14" t="s">
         <v>50</v>
@@ -62093,7 +62087,7 @@
         <v>146</v>
       </c>
       <c r="AP396" s="17" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="AQ396" s="12"/>
       <c r="AR396" s="12"/>
@@ -62118,7 +62112,7 @@
     <row r="397" ht="15.75" customHeight="1">
       <c r="A397" s="13"/>
       <c r="B397" s="14" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
       <c r="C397" s="15"/>
       <c r="D397" s="16" t="s">
@@ -62138,49 +62132,49 @@
       </c>
       <c r="I397" s="15"/>
       <c r="J397" s="14" t="s">
+        <v>1595</v>
+      </c>
+      <c r="K397" s="14" t="s">
+        <v>1596</v>
+      </c>
+      <c r="L397" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="M397" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="N397" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="O397" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="P397" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q397" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="R397" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="S397" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="T397" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="U397" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="V397" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="W397" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="X397" s="14" t="s">
         <v>1597</v>
-      </c>
-      <c r="K397" s="14" t="s">
-        <v>1598</v>
-      </c>
-      <c r="L397" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="M397" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="N397" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="O397" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="P397" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q397" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="R397" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="S397" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="T397" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="U397" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="V397" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="W397" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="X397" s="14" t="s">
-        <v>1599</v>
       </c>
       <c r="Y397" s="14" t="s">
         <v>52</v>
@@ -62234,7 +62228,7 @@
         <v>146</v>
       </c>
       <c r="AP397" s="17" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
       <c r="AQ397" s="12"/>
       <c r="AR397" s="12"/>
@@ -62259,7 +62253,7 @@
     <row r="398" ht="15.75" customHeight="1">
       <c r="A398" s="13"/>
       <c r="B398" s="14" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="C398" s="15"/>
       <c r="D398" s="16" t="s">
@@ -62279,10 +62273,10 @@
       </c>
       <c r="I398" s="15"/>
       <c r="J398" s="14" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="K398" s="14" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="L398" s="14" t="s">
         <v>51</v>
@@ -62375,7 +62369,7 @@
         <v>146</v>
       </c>
       <c r="AP398" s="17" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="AQ398" s="12"/>
       <c r="AR398" s="12"/>
@@ -62400,7 +62394,7 @@
     <row r="399" ht="15.75" customHeight="1">
       <c r="A399" s="13"/>
       <c r="B399" s="14" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="C399" s="15"/>
       <c r="D399" s="16" t="s">
@@ -62419,13 +62413,13 @@
         <v>146</v>
       </c>
       <c r="I399" s="14" t="s">
+        <v>1604</v>
+      </c>
+      <c r="J399" s="14" t="s">
+        <v>1605</v>
+      </c>
+      <c r="K399" s="14" t="s">
         <v>1606</v>
-      </c>
-      <c r="J399" s="14" t="s">
-        <v>1607</v>
-      </c>
-      <c r="K399" s="14" t="s">
-        <v>1608</v>
       </c>
       <c r="L399" s="14" t="s">
         <v>52</v>
@@ -62518,7 +62512,7 @@
         <v>146</v>
       </c>
       <c r="AP399" s="17" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="AQ399" s="12"/>
       <c r="AR399" s="12"/>
@@ -62543,7 +62537,7 @@
     <row r="400" ht="15.75" customHeight="1">
       <c r="A400" s="13"/>
       <c r="B400" s="14" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="C400" s="15"/>
       <c r="D400" s="16" t="s">
@@ -62563,10 +62557,10 @@
       </c>
       <c r="I400" s="15"/>
       <c r="J400" s="14" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="K400" s="14" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="L400" s="14" t="s">
         <v>50</v>
@@ -62659,7 +62653,7 @@
         <v>310</v>
       </c>
       <c r="AP400" s="17" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="AQ400" s="12"/>
       <c r="AR400" s="12"/>
@@ -62684,7 +62678,7 @@
     <row r="401" ht="15.75" customHeight="1">
       <c r="A401" s="13"/>
       <c r="B401" s="14" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="C401" s="15"/>
       <c r="D401" s="16" t="s">
@@ -62704,10 +62698,10 @@
       </c>
       <c r="I401" s="15"/>
       <c r="J401" s="14" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="K401" s="14" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="L401" s="14" t="s">
         <v>51</v>
@@ -62800,7 +62794,7 @@
         <v>146</v>
       </c>
       <c r="AP401" s="17" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="AQ401" s="12"/>
       <c r="AR401" s="12"/>
@@ -62825,7 +62819,7 @@
     <row r="402" ht="15.75" customHeight="1">
       <c r="A402" s="13"/>
       <c r="B402" s="14" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="C402" s="15"/>
       <c r="D402" s="16" t="s">
@@ -62845,10 +62839,10 @@
       </c>
       <c r="I402" s="15"/>
       <c r="J402" s="14" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="K402" s="14" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="L402" s="14" t="s">
         <v>51</v>
@@ -62941,7 +62935,7 @@
         <v>146</v>
       </c>
       <c r="AP402" s="17" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="AQ402" s="12"/>
       <c r="AR402" s="12"/>
@@ -62966,7 +62960,7 @@
     <row r="403" ht="15.75" customHeight="1">
       <c r="A403" s="18"/>
       <c r="B403" s="14" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="C403" s="15"/>
       <c r="D403" s="16" t="s">
@@ -62986,10 +62980,10 @@
       </c>
       <c r="I403" s="15"/>
       <c r="J403" s="14" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="K403" s="14" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="L403" s="14" t="s">
         <v>50</v>
@@ -63082,7 +63076,7 @@
         <v>146</v>
       </c>
       <c r="AP403" s="17" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="AQ403" s="12"/>
       <c r="AR403" s="12"/>
@@ -63107,7 +63101,7 @@
     <row r="404" ht="15.75" customHeight="1">
       <c r="A404" s="13"/>
       <c r="B404" s="14" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="C404" s="15"/>
       <c r="D404" s="16" t="s">
@@ -63127,10 +63121,10 @@
       </c>
       <c r="I404" s="15"/>
       <c r="J404" s="14" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="K404" s="14" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="L404" s="14" t="s">
         <v>52</v>
@@ -63223,7 +63217,7 @@
         <v>146</v>
       </c>
       <c r="AP404" s="17" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="AQ404" s="12"/>
       <c r="AR404" s="12"/>
@@ -63248,7 +63242,7 @@
     <row r="405" ht="15.75" customHeight="1">
       <c r="A405" s="18"/>
       <c r="B405" s="14" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="C405" s="15"/>
       <c r="D405" s="16" t="s">
@@ -63268,10 +63262,10 @@
       </c>
       <c r="I405" s="15"/>
       <c r="J405" s="14" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="K405" s="14" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="L405" s="14" t="s">
         <v>50</v>
@@ -63364,7 +63358,7 @@
         <v>146</v>
       </c>
       <c r="AP405" s="17" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="AQ405" s="12"/>
       <c r="AR405" s="12"/>
@@ -63389,7 +63383,7 @@
     <row r="406" ht="15.75" customHeight="1">
       <c r="A406" s="18"/>
       <c r="B406" s="14" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="C406" s="15"/>
       <c r="D406" s="16" t="s">
@@ -63409,10 +63403,10 @@
       </c>
       <c r="I406" s="15"/>
       <c r="J406" s="14" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="K406" s="14" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="L406" s="14" t="s">
         <v>50</v>
@@ -63505,7 +63499,7 @@
         <v>310</v>
       </c>
       <c r="AP406" s="17" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
       <c r="AQ406" s="12"/>
       <c r="AR406" s="12"/>
@@ -63530,7 +63524,7 @@
     <row r="407" ht="15.75" customHeight="1">
       <c r="A407" s="18"/>
       <c r="B407" s="14" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
       <c r="C407" s="15"/>
       <c r="D407" s="16" t="s">
@@ -63550,10 +63544,10 @@
       </c>
       <c r="I407" s="15"/>
       <c r="J407" s="14" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
       <c r="K407" s="14" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
       <c r="L407" s="14" t="s">
         <v>52</v>
@@ -63646,7 +63640,7 @@
         <v>146</v>
       </c>
       <c r="AP407" s="17" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="AQ407" s="12"/>
       <c r="AR407" s="12"/>
@@ -63671,10 +63665,10 @@
     <row r="408" ht="15.75" customHeight="1">
       <c r="A408" s="18"/>
       <c r="B408" s="14" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
       <c r="C408" s="14" t="s">
-        <v>1643</v>
+        <v>1641</v>
       </c>
       <c r="D408" s="16" t="s">
         <v>43</v>
@@ -63693,10 +63687,10 @@
       </c>
       <c r="I408" s="15"/>
       <c r="J408" s="14" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
       <c r="K408" s="14" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="L408" s="14" t="s">
         <v>50</v>
@@ -63789,7 +63783,7 @@
         <v>146</v>
       </c>
       <c r="AP408" s="17" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
       <c r="AQ408" s="12"/>
       <c r="AR408" s="12"/>
@@ -63814,7 +63808,7 @@
     <row r="409" ht="15.75" customHeight="1">
       <c r="A409" s="18"/>
       <c r="B409" s="14" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="C409" s="15"/>
       <c r="D409" s="16" t="s">
@@ -63834,37 +63828,37 @@
       </c>
       <c r="I409" s="15"/>
       <c r="J409" s="14" t="s">
+        <v>1646</v>
+      </c>
+      <c r="K409" s="14" t="s">
+        <v>1647</v>
+      </c>
+      <c r="L409" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="M409" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="N409" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="O409" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="P409" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q409" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="R409" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="S409" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="T409" s="14" t="s">
         <v>1648</v>
-      </c>
-      <c r="K409" s="14" t="s">
-        <v>1649</v>
-      </c>
-      <c r="L409" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="M409" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="N409" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="O409" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="P409" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q409" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="R409" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="S409" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="T409" s="14" t="s">
-        <v>1650</v>
       </c>
       <c r="U409" s="14" t="s">
         <v>52</v>
@@ -63930,7 +63924,7 @@
         <v>146</v>
       </c>
       <c r="AP409" s="17" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="AQ409" s="12"/>
       <c r="AR409" s="12"/>
@@ -63955,7 +63949,7 @@
     <row r="410" ht="15.75" customHeight="1">
       <c r="A410" s="18"/>
       <c r="B410" s="14" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="C410" s="15"/>
       <c r="D410" s="16" t="s">
@@ -63975,10 +63969,10 @@
       </c>
       <c r="I410" s="15"/>
       <c r="J410" s="14" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="K410" s="14" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="L410" s="14" t="s">
         <v>51</v>
@@ -64071,7 +64065,7 @@
         <v>146</v>
       </c>
       <c r="AP410" s="17" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
       <c r="AQ410" s="12"/>
       <c r="AR410" s="12"/>
@@ -64096,7 +64090,7 @@
     <row r="411" ht="15.75" customHeight="1">
       <c r="A411" s="18"/>
       <c r="B411" s="14" t="s">
-        <v>1656</v>
+        <v>1654</v>
       </c>
       <c r="C411" s="15"/>
       <c r="D411" s="16" t="s">
@@ -64116,10 +64110,10 @@
       </c>
       <c r="I411" s="15"/>
       <c r="J411" s="14" t="s">
-        <v>1657</v>
+        <v>1655</v>
       </c>
       <c r="K411" s="14" t="s">
-        <v>1658</v>
+        <v>1656</v>
       </c>
       <c r="L411" s="14" t="s">
         <v>51</v>
@@ -64212,7 +64206,7 @@
         <v>1146</v>
       </c>
       <c r="AP411" s="17" t="s">
-        <v>1659</v>
+        <v>1657</v>
       </c>
       <c r="AQ411" s="12"/>
       <c r="AR411" s="12"/>
@@ -64237,7 +64231,7 @@
     <row r="412" ht="15.75" customHeight="1">
       <c r="A412" s="18"/>
       <c r="B412" s="14" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
       <c r="C412" s="15"/>
       <c r="D412" s="16" t="s">
@@ -64257,10 +64251,10 @@
       </c>
       <c r="I412" s="15"/>
       <c r="J412" s="14" t="s">
-        <v>1661</v>
+        <v>1659</v>
       </c>
       <c r="K412" s="14" t="s">
-        <v>1662</v>
+        <v>1660</v>
       </c>
       <c r="L412" s="14" t="s">
         <v>51</v>
@@ -64353,7 +64347,7 @@
         <v>146</v>
       </c>
       <c r="AP412" s="17" t="s">
-        <v>1663</v>
+        <v>1661</v>
       </c>
       <c r="AQ412" s="12"/>
       <c r="AR412" s="12"/>
@@ -64378,7 +64372,7 @@
     <row r="413" ht="15.75" customHeight="1">
       <c r="A413" s="18"/>
       <c r="B413" s="14" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
       <c r="C413" s="15"/>
       <c r="D413" s="16" t="s">
@@ -64400,10 +64394,10 @@
         <v>85</v>
       </c>
       <c r="J413" s="14" t="s">
-        <v>1664</v>
+        <v>1662</v>
       </c>
       <c r="K413" s="14" t="s">
-        <v>1665</v>
+        <v>1663</v>
       </c>
       <c r="L413" s="14" t="s">
         <v>51</v>
@@ -64496,7 +64490,7 @@
         <v>146</v>
       </c>
       <c r="AP413" s="17" t="s">
-        <v>1663</v>
+        <v>1661</v>
       </c>
       <c r="AQ413" s="12"/>
       <c r="AR413" s="12"/>
@@ -64521,7 +64515,7 @@
     <row r="414" ht="15.75" customHeight="1">
       <c r="A414" s="18"/>
       <c r="B414" s="14" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
       <c r="C414" s="15"/>
       <c r="D414" s="16" t="s">
@@ -64543,10 +64537,10 @@
         <v>165</v>
       </c>
       <c r="J414" s="14" t="s">
-        <v>1666</v>
+        <v>1664</v>
       </c>
       <c r="K414" s="14" t="s">
-        <v>1667</v>
+        <v>1665</v>
       </c>
       <c r="L414" s="14" t="s">
         <v>52</v>
@@ -64639,7 +64633,7 @@
         <v>146</v>
       </c>
       <c r="AP414" s="63" t="s">
-        <v>1663</v>
+        <v>1661</v>
       </c>
       <c r="AQ414" s="12"/>
       <c r="AR414" s="12"/>
@@ -64664,7 +64658,7 @@
     <row r="415" ht="15.75" customHeight="1">
       <c r="A415" s="18"/>
       <c r="B415" s="14" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="C415" s="15"/>
       <c r="D415" s="16" t="s">
@@ -64686,10 +64680,10 @@
         <v>267</v>
       </c>
       <c r="J415" s="14" t="s">
-        <v>1669</v>
+        <v>1667</v>
       </c>
       <c r="K415" s="14" t="s">
-        <v>1670</v>
+        <v>1668</v>
       </c>
       <c r="L415" s="14" t="s">
         <v>50</v>
@@ -64782,7 +64776,7 @@
         <v>146</v>
       </c>
       <c r="AP415" s="64" t="s">
-        <v>1671</v>
+        <v>1669</v>
       </c>
       <c r="AQ415" s="12"/>
       <c r="AR415" s="12"/>
@@ -64807,7 +64801,7 @@
     <row r="416" ht="15.75" customHeight="1">
       <c r="A416" s="18"/>
       <c r="B416" s="14" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="C416" s="15"/>
       <c r="D416" s="16" t="s">
@@ -64829,10 +64823,10 @@
         <v>264</v>
       </c>
       <c r="J416" s="14" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="K416" s="14" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="L416" s="14" t="s">
         <v>50</v>
@@ -64925,7 +64919,7 @@
         <v>146</v>
       </c>
       <c r="AP416" s="17" t="s">
-        <v>1671</v>
+        <v>1669</v>
       </c>
       <c r="AQ416" s="12"/>
       <c r="AR416" s="12"/>
@@ -64950,7 +64944,7 @@
     <row r="417" ht="15.75" customHeight="1">
       <c r="A417" s="18"/>
       <c r="B417" s="14" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="C417" s="15"/>
       <c r="D417" s="16" t="s">
@@ -64972,10 +64966,10 @@
         <v>270</v>
       </c>
       <c r="J417" s="14" t="s">
-        <v>1674</v>
+        <v>1672</v>
       </c>
       <c r="K417" s="14" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
       <c r="L417" s="14" t="s">
         <v>50</v>
@@ -65068,7 +65062,7 @@
         <v>146</v>
       </c>
       <c r="AP417" s="17" t="s">
-        <v>1671</v>
+        <v>1669</v>
       </c>
       <c r="AQ417" s="12"/>
       <c r="AR417" s="12"/>
@@ -65093,7 +65087,7 @@
     <row r="418" ht="15.75" customHeight="1">
       <c r="A418" s="13"/>
       <c r="B418" s="14" t="s">
-        <v>1676</v>
+        <v>1674</v>
       </c>
       <c r="C418" s="15"/>
       <c r="D418" s="16" t="s">
@@ -65113,10 +65107,10 @@
       </c>
       <c r="I418" s="15"/>
       <c r="J418" s="14" t="s">
-        <v>1677</v>
+        <v>1675</v>
       </c>
       <c r="K418" s="14" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="L418" s="14" t="s">
         <v>50</v>
@@ -65209,7 +65203,7 @@
         <v>146</v>
       </c>
       <c r="AP418" s="17" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="AQ418" s="12"/>
       <c r="AR418" s="12"/>
@@ -65234,7 +65228,7 @@
     <row r="419" ht="15.75" customHeight="1">
       <c r="A419" s="18"/>
       <c r="B419" s="14" t="s">
-        <v>1676</v>
+        <v>1674</v>
       </c>
       <c r="C419" s="15"/>
       <c r="D419" s="16" t="s">
@@ -65256,10 +65250,10 @@
         <v>264</v>
       </c>
       <c r="J419" s="14" t="s">
-        <v>1680</v>
+        <v>1678</v>
       </c>
       <c r="K419" s="14" t="s">
-        <v>1681</v>
+        <v>1679</v>
       </c>
       <c r="L419" s="14" t="s">
         <v>50</v>
@@ -65352,7 +65346,7 @@
         <v>146</v>
       </c>
       <c r="AP419" s="17" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="AQ419" s="12"/>
       <c r="AR419" s="12"/>
@@ -65377,7 +65371,7 @@
     <row r="420" ht="15.75" customHeight="1">
       <c r="A420" s="13"/>
       <c r="B420" s="14" t="s">
-        <v>1676</v>
+        <v>1674</v>
       </c>
       <c r="C420" s="15"/>
       <c r="D420" s="16" t="s">
@@ -65399,10 +65393,10 @@
         <v>270</v>
       </c>
       <c r="J420" s="14" t="s">
-        <v>1682</v>
+        <v>1680</v>
       </c>
       <c r="K420" s="14" t="s">
-        <v>1683</v>
+        <v>1681</v>
       </c>
       <c r="L420" s="14" t="s">
         <v>50</v>
@@ -65495,7 +65489,7 @@
         <v>146</v>
       </c>
       <c r="AP420" s="17" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="AQ420" s="12"/>
       <c r="AR420" s="12"/>
@@ -65520,7 +65514,7 @@
     <row r="421" ht="15.75" customHeight="1">
       <c r="A421" s="13"/>
       <c r="B421" s="14" t="s">
-        <v>1684</v>
+        <v>1682</v>
       </c>
       <c r="C421" s="15"/>
       <c r="D421" s="16" t="s">
@@ -65540,10 +65534,10 @@
       </c>
       <c r="I421" s="15"/>
       <c r="J421" s="14" t="s">
-        <v>1685</v>
+        <v>1683</v>
       </c>
       <c r="K421" s="14" t="s">
-        <v>1686</v>
+        <v>1684</v>
       </c>
       <c r="L421" s="14" t="s">
         <v>50</v>
@@ -65636,7 +65630,7 @@
         <v>146</v>
       </c>
       <c r="AP421" s="17" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="AQ421" s="12"/>
       <c r="AR421" s="12"/>
@@ -65661,7 +65655,7 @@
     <row r="422" ht="15.75" customHeight="1">
       <c r="A422" s="13"/>
       <c r="B422" s="14" t="s">
-        <v>1684</v>
+        <v>1682</v>
       </c>
       <c r="C422" s="15"/>
       <c r="D422" s="16" t="s">
@@ -65683,10 +65677,10 @@
         <v>267</v>
       </c>
       <c r="J422" s="14" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
       <c r="K422" s="14" t="s">
-        <v>1689</v>
+        <v>1687</v>
       </c>
       <c r="L422" s="14" t="s">
         <v>50</v>
@@ -65779,7 +65773,7 @@
         <v>146</v>
       </c>
       <c r="AP422" s="17" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="AQ422" s="12"/>
       <c r="AR422" s="12"/>
@@ -65804,7 +65798,7 @@
     <row r="423" ht="15.75" customHeight="1">
       <c r="A423" s="18"/>
       <c r="B423" s="14" t="s">
-        <v>1684</v>
+        <v>1682</v>
       </c>
       <c r="C423" s="15"/>
       <c r="D423" s="16" t="s">
@@ -65826,10 +65820,10 @@
         <v>264</v>
       </c>
       <c r="J423" s="14" t="s">
-        <v>1690</v>
+        <v>1688</v>
       </c>
       <c r="K423" s="14" t="s">
-        <v>1691</v>
+        <v>1689</v>
       </c>
       <c r="L423" s="14" t="s">
         <v>50</v>
@@ -65922,7 +65916,7 @@
         <v>146</v>
       </c>
       <c r="AP423" s="17" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="AQ423" s="12"/>
       <c r="AR423" s="12"/>
@@ -65947,7 +65941,7 @@
     <row r="424" ht="15.75" customHeight="1">
       <c r="A424" s="13"/>
       <c r="B424" s="14" t="s">
-        <v>1684</v>
+        <v>1682</v>
       </c>
       <c r="C424" s="15"/>
       <c r="D424" s="16" t="s">
@@ -65969,10 +65963,10 @@
         <v>270</v>
       </c>
       <c r="J424" s="14" t="s">
-        <v>1692</v>
+        <v>1690</v>
       </c>
       <c r="K424" s="14" t="s">
-        <v>1693</v>
+        <v>1691</v>
       </c>
       <c r="L424" s="14" t="s">
         <v>50</v>
@@ -66065,7 +66059,7 @@
         <v>146</v>
       </c>
       <c r="AP424" s="17" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="AQ424" s="12"/>
       <c r="AR424" s="12"/>
@@ -66090,7 +66084,7 @@
     <row r="425" ht="15.75" customHeight="1">
       <c r="A425" s="13"/>
       <c r="B425" s="14" t="s">
-        <v>1694</v>
+        <v>1692</v>
       </c>
       <c r="C425" s="26"/>
       <c r="D425" s="16" t="s">
@@ -66110,10 +66104,10 @@
       </c>
       <c r="I425" s="15"/>
       <c r="J425" s="14" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="K425" s="14" t="s">
-        <v>1696</v>
+        <v>1694</v>
       </c>
       <c r="L425" s="14" t="s">
         <v>50</v>
@@ -66206,7 +66200,7 @@
         <v>69</v>
       </c>
       <c r="AP425" s="17" t="s">
-        <v>1697</v>
+        <v>1695</v>
       </c>
       <c r="AQ425" s="12"/>
       <c r="AR425" s="12"/>
@@ -66231,7 +66225,7 @@
     <row r="426" ht="15.75" customHeight="1">
       <c r="A426" s="13"/>
       <c r="B426" s="14" t="s">
-        <v>1698</v>
+        <v>1696</v>
       </c>
       <c r="C426" s="15"/>
       <c r="D426" s="16" t="s">
@@ -66251,10 +66245,10 @@
       </c>
       <c r="I426" s="15"/>
       <c r="J426" s="14" t="s">
-        <v>1699</v>
+        <v>1697</v>
       </c>
       <c r="K426" s="14" t="s">
-        <v>1700</v>
+        <v>1698</v>
       </c>
       <c r="L426" s="14" t="s">
         <v>50</v>
@@ -66347,7 +66341,7 @@
         <v>69</v>
       </c>
       <c r="AP426" s="17" t="s">
-        <v>1701</v>
+        <v>1699</v>
       </c>
       <c r="AQ426" s="12"/>
       <c r="AR426" s="12"/>
@@ -66372,7 +66366,7 @@
     <row r="427" ht="15.75" customHeight="1">
       <c r="A427" s="18"/>
       <c r="B427" s="14" t="s">
-        <v>1702</v>
+        <v>1700</v>
       </c>
       <c r="C427" s="15"/>
       <c r="D427" s="16" t="s">
@@ -66392,10 +66386,10 @@
       </c>
       <c r="I427" s="15"/>
       <c r="J427" s="14" t="s">
-        <v>1703</v>
+        <v>1701</v>
       </c>
       <c r="K427" s="14" t="s">
-        <v>1704</v>
+        <v>1702</v>
       </c>
       <c r="L427" s="14" t="s">
         <v>50</v>
@@ -66488,7 +66482,7 @@
         <v>96</v>
       </c>
       <c r="AP427" s="17" t="s">
-        <v>1705</v>
+        <v>1703</v>
       </c>
       <c r="AQ427" s="12"/>
       <c r="AR427" s="12"/>
@@ -66513,7 +66507,7 @@
     <row r="428" ht="15.75" customHeight="1">
       <c r="A428" s="18"/>
       <c r="B428" s="14" t="s">
-        <v>1706</v>
+        <v>1704</v>
       </c>
       <c r="C428" s="15"/>
       <c r="D428" s="16" t="s">
@@ -66533,10 +66527,10 @@
       </c>
       <c r="I428" s="15"/>
       <c r="J428" s="14" t="s">
-        <v>1707</v>
+        <v>1705</v>
       </c>
       <c r="K428" s="14" t="s">
-        <v>1708</v>
+        <v>1706</v>
       </c>
       <c r="L428" s="14" t="s">
         <v>50</v>
@@ -66654,7 +66648,7 @@
     <row r="429" ht="15.75" customHeight="1">
       <c r="A429" s="18"/>
       <c r="B429" s="14" t="s">
-        <v>1709</v>
+        <v>1707</v>
       </c>
       <c r="C429" s="14" t="s">
         <v>109</v>
@@ -66676,10 +66670,10 @@
       </c>
       <c r="I429" s="15"/>
       <c r="J429" s="14" t="s">
-        <v>1710</v>
+        <v>1708</v>
       </c>
       <c r="K429" s="14" t="s">
-        <v>1711</v>
+        <v>1709</v>
       </c>
       <c r="L429" s="14" t="s">
         <v>50</v>
@@ -66772,7 +66766,7 @@
         <v>89</v>
       </c>
       <c r="AP429" s="17" t="s">
-        <v>1712</v>
+        <v>1710</v>
       </c>
       <c r="AQ429" s="12"/>
       <c r="AR429" s="12"/>
@@ -66797,7 +66791,7 @@
     <row r="430" ht="15.75" customHeight="1">
       <c r="A430" s="18"/>
       <c r="B430" s="14" t="s">
-        <v>1713</v>
+        <v>1711</v>
       </c>
       <c r="C430" s="15"/>
       <c r="D430" s="16" t="s">
@@ -66817,10 +66811,10 @@
       </c>
       <c r="I430" s="15"/>
       <c r="J430" s="14" t="s">
-        <v>1714</v>
+        <v>1712</v>
       </c>
       <c r="K430" s="14" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="L430" s="14" t="s">
         <v>50</v>
@@ -66913,7 +66907,7 @@
         <v>89</v>
       </c>
       <c r="AP430" s="17" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
       <c r="AQ430" s="12"/>
       <c r="AR430" s="12"/>
@@ -66938,7 +66932,7 @@
     <row r="431" ht="15.75" customHeight="1">
       <c r="A431" s="18"/>
       <c r="B431" s="14" t="s">
-        <v>1717</v>
+        <v>1715</v>
       </c>
       <c r="C431" s="15"/>
       <c r="D431" s="16" t="s">
@@ -66958,10 +66952,10 @@
       </c>
       <c r="I431" s="15"/>
       <c r="J431" s="14" t="s">
-        <v>1718</v>
+        <v>1716</v>
       </c>
       <c r="K431" s="14" t="s">
-        <v>1719</v>
+        <v>1717</v>
       </c>
       <c r="L431" s="14" t="s">
         <v>50</v>
@@ -67054,7 +67048,7 @@
         <v>69</v>
       </c>
       <c r="AP431" s="17" t="s">
-        <v>1720</v>
+        <v>1718</v>
       </c>
       <c r="AQ431" s="12"/>
       <c r="AR431" s="12"/>
@@ -67079,7 +67073,7 @@
     <row r="432" ht="15.75" customHeight="1">
       <c r="A432" s="18"/>
       <c r="B432" s="14" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
       <c r="C432" s="15"/>
       <c r="D432" s="16" t="s">
@@ -67099,10 +67093,10 @@
       </c>
       <c r="I432" s="15"/>
       <c r="J432" s="14" t="s">
-        <v>1722</v>
+        <v>1720</v>
       </c>
       <c r="K432" s="14" t="s">
-        <v>1723</v>
+        <v>1721</v>
       </c>
       <c r="L432" s="14" t="s">
         <v>50</v>
@@ -67195,7 +67189,7 @@
         <v>96</v>
       </c>
       <c r="AP432" s="17" t="s">
-        <v>1724</v>
+        <v>1722</v>
       </c>
       <c r="AQ432" s="12"/>
       <c r="AR432" s="12"/>
@@ -67220,7 +67214,7 @@
     <row r="433" ht="15.75" customHeight="1">
       <c r="A433" s="18"/>
       <c r="B433" s="14" t="s">
-        <v>1725</v>
+        <v>1723</v>
       </c>
       <c r="C433" s="15"/>
       <c r="D433" s="16" t="s">
@@ -67240,10 +67234,10 @@
       </c>
       <c r="I433" s="15"/>
       <c r="J433" s="14" t="s">
-        <v>1726</v>
+        <v>1724</v>
       </c>
       <c r="K433" s="14" t="s">
-        <v>1727</v>
+        <v>1725</v>
       </c>
       <c r="L433" s="14" t="s">
         <v>50</v>
@@ -67336,7 +67330,7 @@
         <v>46</v>
       </c>
       <c r="AP433" s="17" t="s">
-        <v>1728</v>
+        <v>1726</v>
       </c>
       <c r="AQ433" s="12"/>
       <c r="AR433" s="12"/>
@@ -67361,7 +67355,7 @@
     <row r="434" ht="15.75" customHeight="1">
       <c r="A434" s="18"/>
       <c r="B434" s="14" t="s">
-        <v>1729</v>
+        <v>1727</v>
       </c>
       <c r="C434" s="15"/>
       <c r="D434" s="16" t="s">
@@ -67381,10 +67375,10 @@
       </c>
       <c r="I434" s="15"/>
       <c r="J434" s="14" t="s">
-        <v>1730</v>
+        <v>1728</v>
       </c>
       <c r="K434" s="14" t="s">
-        <v>1731</v>
+        <v>1729</v>
       </c>
       <c r="L434" s="14" t="s">
         <v>50</v>
@@ -67477,7 +67471,7 @@
         <v>69</v>
       </c>
       <c r="AP434" s="17" t="s">
-        <v>1732</v>
+        <v>1730</v>
       </c>
       <c r="AQ434" s="12"/>
       <c r="AR434" s="12"/>
@@ -67503,7 +67497,7 @@
       <c r="A435" s="65"/>
       <c r="B435" s="15"/>
       <c r="C435" s="66" t="s">
-        <v>1733</v>
+        <v>1731</v>
       </c>
       <c r="D435" s="67"/>
       <c r="E435" s="67"/>
@@ -67518,10 +67512,10 @@
       </c>
       <c r="I435" s="68"/>
       <c r="J435" s="38" t="s">
-        <v>1734</v>
+        <v>1732</v>
       </c>
       <c r="K435" s="38" t="s">
-        <v>1735</v>
+        <v>1733</v>
       </c>
       <c r="L435" s="66" t="s">
         <v>50</v>
@@ -67614,7 +67608,7 @@
         <v>89</v>
       </c>
       <c r="AP435" s="69" t="s">
-        <v>1736</v>
+        <v>1734</v>
       </c>
       <c r="AQ435" s="12"/>
       <c r="AR435" s="12"/>
@@ -67640,7 +67634,7 @@
       <c r="A436" s="65"/>
       <c r="B436" s="15"/>
       <c r="C436" s="66" t="s">
-        <v>1737</v>
+        <v>1735</v>
       </c>
       <c r="D436" s="67"/>
       <c r="E436" s="67"/>
@@ -67655,10 +67649,10 @@
       </c>
       <c r="I436" s="68"/>
       <c r="J436" s="38" t="s">
-        <v>1738</v>
+        <v>1736</v>
       </c>
       <c r="K436" s="38" t="s">
-        <v>1739</v>
+        <v>1737</v>
       </c>
       <c r="L436" s="66" t="s">
         <v>50</v>
@@ -67751,7 +67745,7 @@
         <v>89</v>
       </c>
       <c r="AP436" s="69" t="s">
-        <v>1740</v>
+        <v>1738</v>
       </c>
       <c r="AQ436" s="12"/>
       <c r="AR436" s="12"/>
@@ -67777,7 +67771,7 @@
       <c r="A437" s="65"/>
       <c r="B437" s="15"/>
       <c r="C437" s="66" t="s">
-        <v>1741</v>
+        <v>1739</v>
       </c>
       <c r="D437" s="67"/>
       <c r="E437" s="67"/>
@@ -67792,10 +67786,10 @@
       </c>
       <c r="I437" s="68"/>
       <c r="J437" s="38" t="s">
-        <v>1742</v>
+        <v>1740</v>
       </c>
       <c r="K437" s="38" t="s">
-        <v>1743</v>
+        <v>1741</v>
       </c>
       <c r="L437" s="66" t="s">
         <v>50</v>
@@ -67888,7 +67882,7 @@
         <v>541</v>
       </c>
       <c r="AP437" s="69" t="s">
-        <v>1744</v>
+        <v>1742</v>
       </c>
       <c r="AQ437" s="12"/>
       <c r="AR437" s="12"/>
@@ -67914,7 +67908,7 @@
       <c r="A438" s="65"/>
       <c r="B438" s="15"/>
       <c r="C438" s="66" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
       <c r="D438" s="67"/>
       <c r="E438" s="67"/>
@@ -67929,10 +67923,10 @@
       </c>
       <c r="I438" s="68"/>
       <c r="J438" s="38" t="s">
-        <v>1746</v>
+        <v>1744</v>
       </c>
       <c r="K438" s="38" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="L438" s="66" t="s">
         <v>50</v>
@@ -68025,7 +68019,7 @@
         <v>89</v>
       </c>
       <c r="AP438" s="69" t="s">
-        <v>1748</v>
+        <v>1746</v>
       </c>
       <c r="AQ438" s="12"/>
       <c r="AR438" s="12"/>
@@ -68051,7 +68045,7 @@
       <c r="A439" s="65"/>
       <c r="B439" s="15"/>
       <c r="C439" s="66" t="s">
-        <v>1749</v>
+        <v>1747</v>
       </c>
       <c r="D439" s="67"/>
       <c r="E439" s="67"/>
@@ -68066,10 +68060,10 @@
       </c>
       <c r="I439" s="68"/>
       <c r="J439" s="38" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
       <c r="K439" s="38" t="s">
-        <v>1751</v>
+        <v>1749</v>
       </c>
       <c r="L439" s="66" t="s">
         <v>50</v>
@@ -68162,7 +68156,7 @@
         <v>146</v>
       </c>
       <c r="AP439" s="69" t="s">
-        <v>1752</v>
+        <v>1750</v>
       </c>
       <c r="AQ439" s="12"/>
       <c r="AR439" s="12"/>
